--- a/data/review/audit_T4.xlsx
+++ b/data/review/audit_T4.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R38"/>
+  <dimension ref="A1:S39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,15 +494,20 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>fix</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>audit</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>auditor</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>audit_note</t>
         </is>
@@ -521,7 +526,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Trường hợp quận, thành phố thuộc thành phố trực thuộc trung ương đã có quy hoạch được phê duyệt, loại quy hoạch nào cho phép không phải lập quy hoạch sử dụng đất cấp huyện?</t>
+          <t>Quy hoạch chung hoặc quy hoạch phân khu cho phép quận, thành phố thuộc thành phố trực thuộc trung ương không phải lập quy hoạch sử dụng đất cấp huyện phải được phê duyệt theo pháp luật về lĩnh vực nào?</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -561,24 +566,21 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>group_mismatch</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Loại quy hoạch (quy hoạch chung hoặc quy hoạch phân khu) như nhau ở hai mốc; chỉ đổi tên luật dẫn chiếu (quy hoạch đô thị → quy hoạch đô thị và nông thôn)</t>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Trường hợp quận, thành phố thuộc thành phố trực thuộc trung ương đã có quy hoạch được phê duyệt, loại quy hoạch nào cho phép không phải lập quy hoạch sử dụng đất cấp huyện?»; nhãn cũ khong_dat group_mismatch: Loại quy hoạch (quy hoạch chung hoặc quy hoạch phân khu) như nhau ở hai mốc; chỉ đổi tên luật dẫn chiếu (quy hoạch đô thị → quy hoạch đô thị và nông thôn)). Câu hỏi hỏi pháp luật phê duyệt, chạm chỗ đổi tên luật</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -593,7 +595,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Trường hợp quận, thành phố thuộc thành phố trực thuộc trung ương đã có quy hoạch được phê duyệt, loại quy hoạch nào cho phép không phải lập quy hoạch sử dụng đất cấp huyện?</t>
+          <t>Quy hoạch chung hoặc quy hoạch phân khu cho phép quận, thành phố thuộc thành phố trực thuộc trung ương không phải lập quy hoạch sử dụng đất cấp huyện phải được phê duyệt theo pháp luật về lĩnh vực nào?</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -633,24 +635,21 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>group_mismatch</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Loại quy hoạch (quy hoạch chung hoặc quy hoạch phân khu) như nhau ở hai mốc; chỉ đổi tên luật dẫn chiếu (quy hoạch đô thị → quy hoạch đô thị và nông thôn)</t>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Trường hợp quận, thành phố thuộc thành phố trực thuộc trung ương đã có quy hoạch được phê duyệt, loại quy hoạch nào cho phép không phải lập quy hoạch sử dụng đất cấp huyện?»; nhãn cũ khong_dat group_mismatch: Loại quy hoạch (quy hoạch chung hoặc quy hoạch phân khu) như nhau ở hai mốc; chỉ đổi tên luật dẫn chiếu (quy hoạch đô thị → quy hoạch đô thị và nông thôn)). Câu hỏi hỏi pháp luật phê duyệt, chạm chỗ đổi tên luật</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -724,9 +723,14 @@
           <t>b) Nhân viên của doanh nghiệp giao nhận hàng hóa, bưu gửi bằng đường hàng không;</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>loại lineage (question_ambiguous): Điểm b (doanh nghiệp giao nhận hàng hóa, bưu gửi bằng đường hàng không) và điểm c (doanh nghiệp khảo sát, thi công, sửa chữa, bảo dưỡng tại cảng) cùng khoản cũng là doanh nghiệp có nhân viên được xem xét cấp thẻ dài hạn</t>
+        </is>
+      </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -800,9 +804,14 @@
           <t>b) Nhân viên của doanh nghiệp giao nhận hàng hóa, bưu gửi bằng đường hàng không;</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>loại lineage (question_ambiguous): Điểm b (doanh nghiệp giao nhận hàng hóa, bưu gửi bằng đường hàng không) và điểm c (doanh nghiệp khảo sát, thi công, sửa chữa, bảo dưỡng tại cảng) cùng khoản cũng là doanh nghiệp có nhân viên được xem xét cấp thẻ dài hạn</t>
+        </is>
+      </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -871,6 +880,7 @@
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -935,6 +945,7 @@
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -999,6 +1010,7 @@
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1063,6 +1075,7 @@
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1077,7 +1090,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Theo quy định về di dời trạm định vị vệ tinh, Ủy ban nhân dân cấp tỉnh phối hợp với bộ nào để thực hiện?</t>
+          <t>Khi di dời trạm định vị vệ tinh quốc gia, Ủy ban nhân dân cấp tỉnh phối hợp với bộ nào để tổ chức việc di dời?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1117,28 +1130,21 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>question_ambiguous</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Câu hỏi không nêu trạm quốc gia; điểm đ cùng khoản quy định Ủy ban nhân dân cấp tỉnh phối hợp với bộ, cơ quan ngang bộ, cơ quan thuộc Chính phủ di dời trạm định vị vệ tinh chuyên ngành</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>đ) Ủy ban nhân dân cấp tỉnh phối hợp với bộ, cơ quan ngang bộ, cơ quan thuộc Chính phủ tổ chức việc di dời trạ...</t>
-        </is>
-      </c>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Theo quy định về di dời trạm định vị vệ tinh, Ủy ban nhân dân cấp tỉnh phối hợp với bộ nào để thực hiện?»; nhãn cũ khong_dat question_ambiguous: Câu hỏi không nêu trạm quốc gia; điểm đ cùng khoản quy định Ủy ban nhân dân cấp tỉnh phối hợp với bộ, cơ quan ngang bộ, cơ quan thuộc Chính phủ di dời trạm định vị vệ tinh chuyên ngành). Đã nêu trạm quốc gia, loại điểm đ</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1153,7 +1159,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Theo quy định về di dời trạm định vị vệ tinh, Ủy ban nhân dân cấp tỉnh phối hợp với bộ nào để thực hiện?</t>
+          <t>Khi di dời trạm định vị vệ tinh quốc gia, Ủy ban nhân dân cấp tỉnh phối hợp với bộ nào để tổ chức việc di dời?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1193,28 +1199,21 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>question_ambiguous</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Câu hỏi không nêu trạm quốc gia; điểm đ cùng khoản quy định Ủy ban nhân dân cấp tỉnh phối hợp với bộ, cơ quan ngang bộ, cơ quan thuộc Chính phủ di dời trạm định vị vệ tinh chuyên ngành</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>đ) Ủy ban nhân dân cấp tỉnh phối hợp với bộ, cơ quan ngang bộ, cơ quan thuộc Chính phủ tổ chức việc di dời trạ...</t>
-        </is>
-      </c>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Theo quy định về di dời trạm định vị vệ tinh, Ủy ban nhân dân cấp tỉnh phối hợp với bộ nào để thực hiện?»; nhãn cũ khong_dat question_ambiguous: Câu hỏi không nêu trạm quốc gia; điểm đ cùng khoản quy định Ủy ban nhân dân cấp tỉnh phối hợp với bộ, cơ quan ngang bộ, cơ quan thuộc Chính phủ di dời trạm định vị vệ tinh chuyên ngành). Đã nêu trạm quốc gia, loại điểm đ</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1229,7 +1228,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Khi sĩ quan dự bị vắng mặt tại nơi cư trú từ 30 ngày trở lên, người đó phải báo cáo cho cơ quan quân sự cấp nào và theo thời gian nào?</t>
+          <t>Khi có sĩ quan dự bị vắng mặt tại nơi cư trú, Ban Chỉ huy quân sự cấp xã phải tổng hợp báo cáo lên cơ quan quân sự nào và vào thời gian nào?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1269,24 +1268,21 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>group_mismatch</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Người vắng mặt báo cáo Ban Chỉ huy quân sự cấp xã (hoặc nơi làm việc) ở cả hai mốc; chỗ đổi là việc Ban Chỉ huy quân sự cấp xã tổng hợp báo cáo lên cấp huyện → cấp tỉnh, từ ngày 25 đến 30 hằng tháng</t>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Khi sĩ quan dự bị vắng mặt tại nơi cư trú từ 30 ngày trở lên, người đó phải báo cáo cho cơ quan quân sự cấp nào và theo thời gian nào?»; nhãn cũ khong_dat group_mismatch: Người vắng mặt báo cáo Ban Chỉ huy quân sự cấp xã (hoặc nơi làm việc) ở cả hai mốc; chỗ đổi là việc Ban Chỉ huy quân sự cấp xã tổng hợp báo cáo lên cấp huyện → cấp tỉnh, từ ngày 25 đến 30 hằng tháng). Câu hỏi hỏi nơi nhận và thời gian báo cáo tổng hợp, chạm chỗ đổi</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1301,7 +1297,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Khi sĩ quan dự bị vắng mặt tại nơi cư trú từ 30 ngày trở lên, người đó phải báo cáo cho cơ quan quân sự cấp nào và theo thời gian nào?</t>
+          <t>Khi có sĩ quan dự bị vắng mặt tại nơi cư trú, Ban Chỉ huy quân sự cấp xã phải tổng hợp báo cáo lên cơ quan quân sự nào và vào thời gian nào?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1341,24 +1337,21 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>group_mismatch</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Người vắng mặt báo cáo Ban Chỉ huy quân sự cấp xã (hoặc nơi làm việc) ở cả hai mốc; chỗ đổi là việc Ban Chỉ huy quân sự cấp xã tổng hợp báo cáo lên cấp huyện → cấp tỉnh, từ ngày 25 đến 30 hằng tháng</t>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Khi sĩ quan dự bị vắng mặt tại nơi cư trú từ 30 ngày trở lên, người đó phải báo cáo cho cơ quan quân sự cấp nào và theo thời gian nào?»; nhãn cũ khong_dat group_mismatch: Người vắng mặt báo cáo Ban Chỉ huy quân sự cấp xã (hoặc nơi làm việc) ở cả hai mốc; chỗ đổi là việc Ban Chỉ huy quân sự cấp xã tổng hợp báo cáo lên cấp huyện → cấp tỉnh, từ ngày 25 đến 30 hằng tháng). Câu hỏi hỏi nơi nhận và thời gian báo cáo tổng hợp, chạm chỗ đổi</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1423,6 +1416,7 @@
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1487,6 +1481,7 @@
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1551,6 +1546,7 @@
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1615,6 +1611,7 @@
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1629,7 +1626,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Trường hợp cấp Giấy chứng nhận vùng hoạt động hoa tiêu hàng hải cho một vùng và tuyến dẫn tàu cụ thể, người được cấp phải đáp ứng điều kiện gì về thực tập dẫn tàu?</t>
+          <t>Những người nào được cấp Giấy chứng nhận vùng hoạt động hoa tiêu hàng hải tại một vùng hoạt động và tuyến dẫn tàu căn cứ vào kinh nghiệm đã có tại vùng, tuyến đó?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1669,24 +1666,21 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>group_mismatch</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Với hoa tiêu, điều kiện thực tập dẫn tàu như nhau ở hai mốc; chỗ đổi thêm trường hợp thuyền trưởng đã dẫn tàu, câu hỏi không hỏi</t>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Trường hợp cấp Giấy chứng nhận vùng hoạt động hoa tiêu hàng hải cho một vùng và tuyến dẫn tàu cụ thể, người được cấp phải đáp ứng điều kiện gì về thực tập dẫn tàu?»; nhãn cũ khong_dat group_mismatch: Với hoa tiêu, điều kiện thực tập dẫn tàu như nhau ở hai mốc; chỗ đổi thêm trường hợp thuyền trưởng đã dẫn tàu, câu hỏi không hỏi). Câu hỏi hỏi những người được cấp theo kinh nghiệm, chạm chỗ thêm thuyền trưởng</t>
         </is>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1701,7 +1695,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Trường hợp cấp Giấy chứng nhận vùng hoạt động hoa tiêu hàng hải cho một vùng và tuyến dẫn tàu cụ thể, người được cấp phải đáp ứng điều kiện gì về thực tập dẫn tàu?</t>
+          <t>Những người nào được cấp Giấy chứng nhận vùng hoạt động hoa tiêu hàng hải tại một vùng hoạt động và tuyến dẫn tàu căn cứ vào kinh nghiệm đã có tại vùng, tuyến đó?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1741,24 +1735,21 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>group_mismatch</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Với hoa tiêu, điều kiện thực tập dẫn tàu như nhau ở hai mốc; chỗ đổi thêm trường hợp thuyền trưởng đã dẫn tàu, câu hỏi không hỏi</t>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Trường hợp cấp Giấy chứng nhận vùng hoạt động hoa tiêu hàng hải cho một vùng và tuyến dẫn tàu cụ thể, người được cấp phải đáp ứng điều kiện gì về thực tập dẫn tàu?»; nhãn cũ khong_dat group_mismatch: Với hoa tiêu, điều kiện thực tập dẫn tàu như nhau ở hai mốc; chỗ đổi thêm trường hợp thuyền trưởng đã dẫn tàu, câu hỏi không hỏi). Câu hỏi hỏi những người được cấp theo kinh nghiệm, chạm chỗ thêm thuyền trưởng</t>
         </is>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1773,7 +1764,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Một người lao động Việt Nam đăng ký dự tuyển làm việc cho tổ chức nước ngoài thì văn bằng, chứng chỉ trong hồ sơ được nộp dưới hình thức bản sao nào?</t>
+          <t>Văn bằng, chứng chỉ do nước ngoài cấp trong hồ sơ dự tuyển của người lao động Việt Nam làm việc cho tổ chức nước ngoài phải được dịch ra tiếng Việt và xác nhận bản dịch theo hình thức nào?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1813,24 +1804,21 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>group_mismatch</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Câu hỏi hỏi hình thức bản sao: cả hai mốc đều là bản sao có chứng thực; chỗ đổi là bản dịch văn bằng nước ngoài được công chứng hoặc chứng thực, câu hỏi không hỏi</t>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Một người lao động Việt Nam đăng ký dự tuyển làm việc cho tổ chức nước ngoài thì văn bằng, chứng chỉ trong hồ sơ được nộp dưới hình thức bản sao nào?»; nhãn cũ khong_dat group_mismatch: Câu hỏi hỏi hình thức bản sao: cả hai mốc đều là bản sao có chứng thực; chỗ đổi là bản dịch văn bằng nước ngoài được công chứng hoặc chứng thực, câu hỏi không hỏi). Câu hỏi hỏi hình thức xác nhận bản dịch, chạm chỗ đổi</t>
         </is>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1845,7 +1833,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Một người lao động Việt Nam đăng ký dự tuyển làm việc cho tổ chức nước ngoài thì văn bằng, chứng chỉ trong hồ sơ được nộp dưới hình thức bản sao nào?</t>
+          <t>Văn bằng, chứng chỉ do nước ngoài cấp trong hồ sơ dự tuyển của người lao động Việt Nam làm việc cho tổ chức nước ngoài phải được dịch ra tiếng Việt và xác nhận bản dịch theo hình thức nào?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1885,24 +1873,21 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>group_mismatch</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Câu hỏi hỏi hình thức bản sao: cả hai mốc đều là bản sao có chứng thực; chỗ đổi là bản dịch văn bằng nước ngoài được công chứng hoặc chứng thực, câu hỏi không hỏi</t>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Một người lao động Việt Nam đăng ký dự tuyển làm việc cho tổ chức nước ngoài thì văn bằng, chứng chỉ trong hồ sơ được nộp dưới hình thức bản sao nào?»; nhãn cũ khong_dat group_mismatch: Câu hỏi hỏi hình thức bản sao: cả hai mốc đều là bản sao có chứng thực; chỗ đổi là bản dịch văn bằng nước ngoài được công chứng hoặc chứng thực, câu hỏi không hỏi). Câu hỏi hỏi hình thức xác nhận bản dịch, chạm chỗ đổi</t>
         </is>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1917,7 +1902,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Khi văn bản thông báo kết quả xác định trước mã số, xuất xứ, trị giá hải quan cần được xem xét lại, cơ quan hải quan cấp nào có thẩm quyền đối với văn bản này?</t>
+          <t>Trường hợp tổ chức, cá nhân không đồng ý với kết quả xác định trước mã số, xuất xứ, trị giá hải quan nhưng cần thông quan hàng hóa, kết quả đó do người đứng đầu cơ quan hải quan cấp nào đưa ra và họ phải làm gì để được thông quan?</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1957,28 +1942,21 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>question_ambiguous</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Việc đề nghị xem xét lại văn bản xác định trước là nội dung khoản 5 cùng Điều; khoản 4 chỉ nói văn bản là cơ sở khai hải quan và cách thông quan khi không đồng ý. Câu hỏi 'cơ quan cấp nào có thẩm quyền đối với văn bản cần xem xét lại' khớp khoản 5 hơn</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>5. Trường hợp không đồng ý với nội dung xác định trước mã số, xuất xứ, trị giá hải quan, tổ chức, cá nhân có v...</t>
-        </is>
-      </c>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Khi văn bản thông báo kết quả xác định trước mã số, xuất xứ, trị giá hải quan cần được xem xét lại, cơ quan hải quan cấp nào có thẩm quyền đối với văn bản này?»; nhãn cũ khong_dat question_ambiguous: Việc đề nghị xem xét lại văn bản xác định trước là nội dung khoản 5 cùng Điều; khoản 4 chỉ nói văn bản là cơ sở khai hải quan và cách thông quan khi không đồng ý. Câu hỏi 'cơ quan cấp nào có thẩm quyền đối với văn bản cần xem xét lại' khớp khoản 5 hơn). Câu hỏi không còn hỏi việc xem xét lại (khoản 5); hỏi người ra kết quả và cách thông quan</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1993,7 +1971,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Khi văn bản thông báo kết quả xác định trước mã số, xuất xứ, trị giá hải quan cần được xem xét lại, cơ quan hải quan cấp nào có thẩm quyền đối với văn bản này?</t>
+          <t>Trường hợp tổ chức, cá nhân không đồng ý với kết quả xác định trước mã số, xuất xứ, trị giá hải quan nhưng cần thông quan hàng hóa, kết quả đó do người đứng đầu cơ quan hải quan cấp nào đưa ra và họ phải làm gì để được thông quan?</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2033,28 +2011,21 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>question_ambiguous</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Việc đề nghị xem xét lại văn bản xác định trước là nội dung khoản 5 cùng Điều; khoản 4 chỉ nói văn bản là cơ sở khai hải quan và cách thông quan khi không đồng ý. Câu hỏi 'cơ quan cấp nào có thẩm quyền đối với văn bản cần xem xét lại' khớp khoản 5 hơn</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>5. Trường hợp không đồng ý với nội dung xác định trước mã số, xuất xứ, trị giá hải quan, tổ chức, cá nhân có v...</t>
-        </is>
-      </c>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Khi văn bản thông báo kết quả xác định trước mã số, xuất xứ, trị giá hải quan cần được xem xét lại, cơ quan hải quan cấp nào có thẩm quyền đối với văn bản này?»; nhãn cũ khong_dat question_ambiguous: Việc đề nghị xem xét lại văn bản xác định trước là nội dung khoản 5 cùng Điều; khoản 4 chỉ nói văn bản là cơ sở khai hải quan và cách thông quan khi không đồng ý. Câu hỏi 'cơ quan cấp nào có thẩm quyền đối với văn bản cần xem xét lại' khớp khoản 5 hơn). Câu hỏi không còn hỏi việc xem xét lại (khoản 5); hỏi người ra kết quả và cách thông quan</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2069,7 +2040,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Trường hợp một tổ chức được chỉ định kiểm định phương tiện đo, quyết định chỉ định được gửi tới những cơ quan nào?</t>
+          <t>Sau khi ban hành, quyết định chỉ định tổ chức kiểm định phương tiện đo được gửi tới đâu và được đăng tải trên cổng thông tin điện tử của cơ quan nào?</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2109,24 +2080,21 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>group_mismatch</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Nơi nhận quyết định (tổ chức được chỉ định, Chi cục Tiêu chuẩn Đo lường Chất lượng) như nhau ở hai mốc; chỗ đổi chỉ là cổng thông tin đăng tải (Tổng cục → Ủy ban), câu hỏi không hỏi tới</t>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Trường hợp một tổ chức được chỉ định kiểm định phương tiện đo, quyết định chỉ định được gửi tới những cơ quan nào?»; nhãn cũ khong_dat group_mismatch: Nơi nhận quyết định (tổ chức được chỉ định, Chi cục Tiêu chuẩn Đo lường Chất lượng) như nhau ở hai mốc; chỗ đổi chỉ là cổng thông tin đăng tải (Tổng cục → Ủy ban), câu hỏi không hỏi tới). Câu hỏi nay hỏi cả cổng đăng tải, chạm chỗ đổi Tổng cục → Ủy ban</t>
         </is>
       </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2141,7 +2109,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Trường hợp một tổ chức được chỉ định kiểm định phương tiện đo, quyết định chỉ định được gửi tới những cơ quan nào?</t>
+          <t>Sau khi ban hành, quyết định chỉ định tổ chức kiểm định phương tiện đo được gửi tới đâu và được đăng tải trên cổng thông tin điện tử của cơ quan nào?</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2181,24 +2149,21 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>group_mismatch</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Nơi nhận quyết định (tổ chức được chỉ định, Chi cục Tiêu chuẩn Đo lường Chất lượng) như nhau ở hai mốc; chỗ đổi chỉ là cổng thông tin đăng tải (Tổng cục → Ủy ban), câu hỏi không hỏi tới</t>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Trường hợp một tổ chức được chỉ định kiểm định phương tiện đo, quyết định chỉ định được gửi tới những cơ quan nào?»; nhãn cũ khong_dat group_mismatch: Nơi nhận quyết định (tổ chức được chỉ định, Chi cục Tiêu chuẩn Đo lường Chất lượng) như nhau ở hai mốc; chỗ đổi chỉ là cổng thông tin đăng tải (Tổng cục → Ủy ban), câu hỏi không hỏi tới). Câu hỏi nay hỏi cả cổng đăng tải, chạm chỗ đổi Tổng cục → Ủy ban</t>
         </is>
       </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2213,7 +2178,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Khi Chấp hành viên gửi báo cáo thống kê kết quả thi hành án của kỳ trước, thời hạn chậm nhất là trước ngày nào của kỳ báo cáo kế tiếp?</t>
+          <t>Khi Chấp hành viên của cơ quan thi hành án dân sự không thuộc quân đội gửi báo cáo thống kê kết quả thi hành án của kỳ trước cho Thủ trưởng cơ quan nơi công tác, thời hạn chậm nhất là trước ngày nào của kỳ báo cáo kế tiếp?</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2253,28 +2218,21 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>question_ambiguous</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Câu hỏi không phân biệt Chấp hành viên dân sự (điểm a) với Chấp hành viên thi hành án dân sự trong quân đội (điểm d, vẫn trước ngày 03); ở mốc 2 hai điểm cho hai đáp án khác nhau</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>d) Chậm nhất trước ngày 03 của kỳ báo cáo kế tiếp, Chấp hành viên thi hành án dân sự trong quân đội phải gửi b...</t>
-        </is>
-      </c>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Khi Chấp hành viên gửi báo cáo thống kê kết quả thi hành án của kỳ trước, thời hạn chậm nhất là trước ngày nào của kỳ báo cáo kế tiếp?»; nhãn cũ khong_dat question_ambiguous: Câu hỏi không phân biệt Chấp hành viên dân sự (điểm a) với Chấp hành viên thi hành án dân sự trong quân đội (điểm d, vẫn trước ngày 03); ở mốc 2 hai điểm cho hai đáp án khác nhau). Câu hỏi loại Chấp hành viên trong quân đội (điểm d)</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2289,7 +2247,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Khi Chấp hành viên gửi báo cáo thống kê kết quả thi hành án của kỳ trước, thời hạn chậm nhất là trước ngày nào của kỳ báo cáo kế tiếp?</t>
+          <t>Khi Chấp hành viên của cơ quan thi hành án dân sự không thuộc quân đội gửi báo cáo thống kê kết quả thi hành án của kỳ trước cho Thủ trưởng cơ quan nơi công tác, thời hạn chậm nhất là trước ngày nào của kỳ báo cáo kế tiếp?</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2329,28 +2287,21 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>question_ambiguous</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Câu hỏi không phân biệt Chấp hành viên dân sự (điểm a) với Chấp hành viên thi hành án dân sự trong quân đội (điểm d, vẫn trước ngày 03); ở mốc 2 hai điểm cho hai đáp án khác nhau</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>d) Chậm nhất trước ngày 03 của kỳ báo cáo kế tiếp, Chấp hành viên thi hành án dân sự trong quân đội phải gửi b...</t>
-        </is>
-      </c>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Khi Chấp hành viên gửi báo cáo thống kê kết quả thi hành án của kỳ trước, thời hạn chậm nhất là trước ngày nào của kỳ báo cáo kế tiếp?»; nhãn cũ khong_dat question_ambiguous: Câu hỏi không phân biệt Chấp hành viên dân sự (điểm a) với Chấp hành viên thi hành án dân sự trong quân đội (điểm d, vẫn trước ngày 03); ở mốc 2 hai điểm cho hai đáp án khác nhau). Câu hỏi loại Chấp hành viên trong quân đội (điểm d)</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2365,7 +2316,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Trường hợp đầu tư nâng cao năng lực cho Cảnh sát môi trường, lực lượng này được đầu tư những gì và để đáp ứng yêu cầu công tác nào?</t>
+          <t>Theo quy định về đầu tư nâng cao năng lực, lực lượng cảnh sát nào được đầu tư cơ sở vật chất, phương tiện, thiết bị kỹ thuật để đấu tranh với tội phạm, vi phạm trong lĩnh vực môi trường?</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2405,24 +2356,21 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>group_mismatch</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Nội dung đầu tư và yêu cầu công tác như nhau ở hai mốc; chỉ đổi tên lực lượng</t>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Trường hợp đầu tư nâng cao năng lực cho Cảnh sát môi trường, lực lượng này được đầu tư những gì và để đáp ứng yêu cầu công tác nào?»; nhãn cũ khong_dat group_mismatch: Nội dung đầu tư và yêu cầu công tác như nhau ở hai mốc; chỉ đổi tên lực lượng). Câu hỏi hỏi tên lực lượng, không chép tên</t>
         </is>
       </c>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2437,7 +2385,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Trường hợp đầu tư nâng cao năng lực cho Cảnh sát môi trường, lực lượng này được đầu tư những gì và để đáp ứng yêu cầu công tác nào?</t>
+          <t>Theo quy định về đầu tư nâng cao năng lực, lực lượng cảnh sát nào được đầu tư cơ sở vật chất, phương tiện, thiết bị kỹ thuật để đấu tranh với tội phạm, vi phạm trong lĩnh vực môi trường?</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2477,29 +2425,26 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>group_mismatch</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Nội dung đầu tư và yêu cầu công tác như nhau ở hai mốc; chỉ đổi tên lực lượng</t>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Trường hợp đầu tư nâng cao năng lực cho Cảnh sát môi trường, lực lượng này được đầu tư những gì và để đáp ứng yêu cầu công tác nào?»; nhãn cũ khong_dat group_mismatch: Nội dung đầu tư và yêu cầu công tác như nhau ở hai mốc; chỉ đổi tên lực lượng). Câu hỏi hỏi tên lực lượng, không chép tên</t>
         </is>
       </c>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>vilextime:T4:provision:a324f2cc-df4c-11f0-894a-8ddf853d159d:2024-01-31</t>
+          <t>vilextime:T4:provision:9d44166a-2e81-11f1-8975-ef6a7728f53c:2025-07-20</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2509,37 +2454,37 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Trong lĩnh vực quản lý rừng bền vững, Sở Nông nghiệp và Phát triển nông thôn phải báo cáo kết quả hằng năm trước ngày nào và gửi cho đơn vị nào thuộc Bộ?</t>
+          <t>Trường hợp cần hướng dẫn thực hiện chế độ cho đối tượng mới được bổ sung, những bộ nào phải ban hành thông tư liên tịch?</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2024-01-31</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3. Sở Nông nghiệp và Phát triển nông thôn:</t>
+          <t>Điều 3. Trách nhiệm thi hành</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>c) Hằng năm trước ngày 15 tháng 12, báo cáo Ủy ban nhân dân cấp tỉnh và Bộ Nông nghiệp và Phát triển nông thôn (Tổng cục Lâm nghiệp) kết quả xây dựng và thực hiện phương án quản lý rừng bền vững và cấp chứng chỉ quản lý rừng bền vững trên địa bàn tỉnh.</t>
+          <t>2. Bộ Công an, Bộ Lao động - Thương binh và Xã hội, Bộ Tài chính ban hành Thông tư liên tịch hướng dẫn thực hiện chế độ đối với đối tượng quy định tại khoản 3 Điều 1 Nghị định này.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Điểm c Khoản 3 Điều 18</t>
+          <t>Khoản 2 Điều 3</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>28/2018/TT-BNNPTNT</t>
+          <t>11/2011/NĐ-CP</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=133923</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=26088</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2559,11 +2504,12 @@
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>vilextime:T4:provision:ada68200-2d45-11f1-95b6-e35525714d94:2024-11-21</t>
+          <t>vilextime:T4:provision:a324f2cc-df4c-11f0-894a-8ddf853d159d:2024-01-31</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2573,37 +2519,37 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Pháp luật về xây dựng và áp dụng tiêu chuẩn quy định cơ quan nào phối hợp trong việc xây dựng và thông báo kế hoạch 5 năm xây dựng TCVN?</t>
+          <t>Trong lĩnh vực quản lý rừng bền vững, Sở Nông nghiệp và Phát triển nông thôn phải báo cáo kết quả hằng năm trước ngày nào và gửi cho đơn vị nào thuộc Bộ?</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-01-31</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2. Kế hoạch 5 năm xây dựng TCVN Nội dung kế hoạch 5 năm xây dựng TCVN bao gồm: lĩnh vực, đối tượng cụ thể cần xây dựng TCVN; loại tiêu chuẩn; số lượng TCVN cần xây dựng; thời gian thực hiện; nguồn kinh phí và kinh phí dự kiến. Lập, phê duyệt, điều chỉnh, bổ sung kế hoạch 5 năm xây dựng TCVN thực hiện theo trình tự sau đây:</t>
+          <t>3. Sở Nông nghiệp và Phát triển nông thôn:</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>c) Phê duyệt kế hoạch 5 năm Bộ trưởng Bộ Khoa học và Công nghệ tổ chức xem xét, phê duyệt kế hoạch 5 năm xây dựng TCVN. Bộ Khoa học và Công nghệ thông báo kế hoạch đã được phê duyệt đến các bộ, ngành, tổ chức liên quan và công khai trên Cổng thông tin điện tử của Bộ Khoa học và Công nghệ, Cổng thông tin điện tử của Tổng cục Tiêu chuẩn Đo lường Chất lượng trong thời hạn 30 (ba mươi) ngày, kể từ ngày kế hoạch được phê duyệt;</t>
+          <t>c) Hằng năm trước ngày 15 tháng 12, báo cáo Ủy ban nhân dân cấp tỉnh và Bộ Nông nghiệp và Phát triển nông thôn (Tổng cục Lâm nghiệp) kết quả xây dựng và thực hiện phương án quản lý rừng bền vững và cấp chứng chỉ quản lý rừng bền vững trên địa bàn tỉnh.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Điểm c Khoản 2 Điều 4</t>
+          <t>Điểm c Khoản 3 Điều 18</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>11/2021/TT-BKHCN</t>
+          <t>28/2018/TT-BNNPTNT</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=152575</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=133923</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2613,33 +2559,22 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>question_ambiguous</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>'Cơ quan nào phối hợp trong việc xây dựng và thông báo kế hoạch' không ghim được chỗ đổi (cổng thông tin công khai); điểm b cùng khoản giao Tổng cục lấy ý kiến, hoàn chỉnh dự thảo kế hoạch, và điểm c do Bộ trưởng phê duyệt, Bộ thông báo</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>b) Lấy ý kiến và hoàn chỉnh dự thảo kế hoạch 5 năm Tổng cục Tiêu chuẩn Đo lường Chất lượng thực hiện các nhiệm...</t>
-        </is>
-      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>vilextime:T4:provision:ada68200-2d45-11f1-95b6-e35525714d94:2024-11-22</t>
+          <t>vilextime:T4:provision:ada68200-2d45-11f1-95b6-e35525714d94:2024-11-21</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2649,12 +2584,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Pháp luật về xây dựng và áp dụng tiêu chuẩn quy định cơ quan nào phối hợp trong việc xây dựng và thông báo kế hoạch 5 năm xây dựng TCVN?</t>
+          <t>Sau khi kế hoạch 5 năm xây dựng TCVN được phê duyệt, kế hoạch phải được công khai trên cổng thông tin điện tử của những cơ quan nào và trong thời hạn bao lâu?</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2664,7 +2599,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>c) Phê duyệt kế hoạch 5 năm Bộ trưởng Bộ Khoa học và Công nghệ tổ chức xem xét, phê duyệt kế hoạch 5 năm xây dựng TCVN. Bộ Khoa học và Công nghệ thông báo kế hoạch đã được phê duyệt đến các bộ, ngành, tổ chức liên quan và công khai trên Cổng thông tin điện tử của Bộ Khoa học và Công nghệ, Cổng thông tin điện tử của Ủy ban Tiêu chuẩn Đo lường Chất lượng Quốc gia trong thời hạn 30 (ba mươi) ngày, kể từ ngày kế hoạch được phê duyệt;</t>
+          <t>c) Phê duyệt kế hoạch 5 năm Bộ trưởng Bộ Khoa học và Công nghệ tổ chức xem xét, phê duyệt kế hoạch 5 năm xây dựng TCVN. Bộ Khoa học và Công nghệ thông báo kế hoạch đã được phê duyệt đến các bộ, ngành, tổ chức liên quan và công khai trên Cổng thông tin điện tử của Bộ Khoa học và Công nghệ, Cổng thông tin điện tử của Tổng cục Tiêu chuẩn Đo lường Chất lượng trong thời hạn 30 (ba mươi) ngày, kể từ ngày kế hoạch được phê duyệt;</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2689,33 +2624,26 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>question_ambiguous</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>'Cơ quan nào phối hợp trong việc xây dựng và thông báo kế hoạch' không ghim được chỗ đổi (cổng thông tin công khai); điểm b cùng khoản giao Tổng cục lấy ý kiến, hoàn chỉnh dự thảo kế hoạch, và điểm c do Bộ trưởng phê duyệt, Bộ thông báo</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>b) Lấy ý kiến và hoàn chỉnh dự thảo kế hoạch 5 năm Tổng cục Tiêu chuẩn Đo lường Chất lượng thực hiện các nhiệm...</t>
-        </is>
-      </c>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Pháp luật về xây dựng và áp dụng tiêu chuẩn quy định cơ quan nào phối hợp trong việc xây dựng và thông báo kế hoạch 5 năm xây dựng TCVN?»; nhãn cũ khong_dat question_ambiguous: 'Cơ quan nào phối hợp trong việc xây dựng và thông báo kế hoạch' không ghim được chỗ đổi (cổng thông tin công khai); điểm b cùng khoản giao Tổng cục lấy ý kiến, hoàn chỉnh dự thảo kế hoạch, và điểm c do Bộ trưởng phê duyệt, Bộ thông báo). Câu hỏi chốt việc công khai sau phê duyệt (điểm c), chạm chỗ đổi</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>vilextime:T4:provision:bcce4ee0-2f37-11f1-927e-c7ac35ffa800:2024-11-14</t>
+          <t>vilextime:T4:provision:ada68200-2d45-11f1-95b6-e35525714d94:2024-11-22</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2725,37 +2653,37 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Thẩm quyền áp dụng biện pháp khắc phục hậu quả của Chủ tịch Ủy ban nhân dân cấp huyện trong lĩnh vực bổ trợ tư pháp được xác định ra sao?</t>
+          <t>Sau khi kế hoạch 5 năm xây dựng TCVN được phê duyệt, kế hoạch phải được công khai trên cổng thông tin điện tử của những cơ quan nào và trong thời hạn bao lâu?</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2. Chủ tịch Ủy ban nhân dân cấp huyện có quyền:</t>
+          <t>2. Kế hoạch 5 năm xây dựng TCVN Nội dung kế hoạch 5 năm xây dựng TCVN bao gồm: lĩnh vực, đối tượng cụ thể cần xây dựng TCVN; loại tiêu chuẩn; số lượng TCVN cần xây dựng; thời gian thực hiện; nguồn kinh phí và kinh phí dự kiến. Lập, phê duyệt, điều chỉnh, bổ sung kế hoạch 5 năm xây dựng TCVN thực hiện theo trình tự sau đây:</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>d) Áp dụng biện pháp khắc phục hậu quả quy định tại các điểm a, e và i khoản 1 Điều 28 Luật Xử lý vi phạm hành chính; các điểm a, b, đ, l, m và n khoản 3 Điều 3 Nghị định này.</t>
+          <t>c) Phê duyệt kế hoạch 5 năm Bộ trưởng Bộ Khoa học và Công nghệ tổ chức xem xét, phê duyệt kế hoạch 5 năm xây dựng TCVN. Bộ Khoa học và Công nghệ thông báo kế hoạch đã được phê duyệt đến các bộ, ngành, tổ chức liên quan và công khai trên Cổng thông tin điện tử của Bộ Khoa học và Công nghệ, Cổng thông tin điện tử của Ủy ban Tiêu chuẩn Đo lường Chất lượng Quốc gia trong thời hạn 30 (ba mươi) ngày, kể từ ngày kế hoạch được phê duyệt;</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Điểm d Khoản 2 Điều 83</t>
+          <t>Điểm c Khoản 2 Điều 4</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>82/2020/NĐ-CP</t>
+          <t>11/2021/TT-BKHCN</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=143024</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=152575</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2770,16 +2698,21 @@
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Pháp luật về xây dựng và áp dụng tiêu chuẩn quy định cơ quan nào phối hợp trong việc xây dựng và thông báo kế hoạch 5 năm xây dựng TCVN?»; nhãn cũ khong_dat question_ambiguous: 'Cơ quan nào phối hợp trong việc xây dựng và thông báo kế hoạch' không ghim được chỗ đổi (cổng thông tin công khai); điểm b cùng khoản giao Tổng cục lấy ý kiến, hoàn chỉnh dự thảo kế hoạch, và điểm c do Bộ trưởng phê duyệt, Bộ thông báo). Câu hỏi chốt việc công khai sau phê duyệt (điểm c), chạm chỗ đổi</t>
+        </is>
+      </c>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>vilextime:T4:provision:bdb196ac-df3f-11f0-a53b-49fbe419b389:2025-06-23</t>
+          <t>vilextime:T4:provision:bcce4ee0-2f37-11f1-927e-c7ac35ffa800:2024-11-14</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2789,37 +2722,37 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Khi hoạt động của bãi cất, hạ cánh trên boong tàu vi phạm điều kiện, quyết định đóng bãi phải được thông báo cho những bộ nào?</t>
+          <t>Thẩm quyền áp dụng biện pháp khắc phục hậu quả của Chủ tịch Ủy ban nhân dân cấp huyện trong lĩnh vực bổ trợ tư pháp được xác định ra sao?</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Điều 16. Trình tự, thủ tục đóng bãi cất, hạ cánh trên boong tàu</t>
+          <t>2. Chủ tịch Ủy ban nhân dân cấp huyện có quyền:</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>3. Khi hoạt động của bãi cất, hạ cánh vi phạm một trong các điều kiện quy định tại điểm a, b, c, d, đ của khoản 2 Điều 10; Bộ Tổng Tham mưu ra quyết định đóng bãi cất, hạ cánh và thông báo với Bộ Xây dựng, chủ sở hữu tàu và các cơ quan, tổ chức, cá nhân liên quan.</t>
+          <t>d) Áp dụng biện pháp khắc phục hậu quả quy định tại các điểm a, e và i khoản 1 Điều 28 Luật Xử lý vi phạm hành chính; các điểm a, b, đ, l, m và n khoản 3 Điều 3 Nghị định này.</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Khoản 3 Điều 16</t>
+          <t>Điểm d Khoản 2 Điều 83</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>42/2016/NĐ-CP</t>
+          <t>82/2020/NĐ-CP</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=141668</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=143024</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2839,11 +2772,12 @@
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>vilextime:T4:provision:dcf457d0-3b96-11f1-b174-b5c1cf7b0c30:2026-08-09</t>
+          <t>vilextime:T4:provision:bdb196ac-df3f-11f0-a53b-49fbe419b389:2025-06-23</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2853,37 +2787,37 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Khi Ủy ban nhân dân cấp tỉnh thực hiện nhiệm vụ quản lý vận tải đường bộ, cơ quan chuyên môn về giao thông ở địa phương được gọi tên theo sở nào?</t>
+          <t>Khi hoạt động của bãi cất, hạ cánh trên boong tàu vi phạm điều kiện, quyết định đóng bãi phải được thông báo cho những bộ nào?</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Điều 73. Ủy ban nhân dân cấp tỉnh</t>
+          <t>Điều 16. Trình tự, thủ tục đóng bãi cất, hạ cánh trên boong tàu</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2. Phối hợp với Ủy ban nhân dân cấp tỉnh có tuyến xe buýt đi qua để thống nhất thực hiện các nhiệm vụ nêu tại khoản 3 Điều 5 của Nghị định này. Thống nhất với Bộ Giao thông vận tải trước khi mở tuyến xe buýt có điểm đầu hoặc điểm cuối nằm trong khu vực cảng hàng không.</t>
+          <t>3. Khi hoạt động của bãi cất, hạ cánh vi phạm một trong các điều kiện quy định tại điểm a, b, c, d, đ của khoản 2 Điều 10; Bộ Tổng Tham mưu ra quyết định đóng bãi cất, hạ cánh và thông báo với Bộ Xây dựng, chủ sở hữu tàu và các cơ quan, tổ chức, cá nhân liên quan.</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Khoản 2 Điều 73</t>
+          <t>Khoản 3 Điều 16</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>158/2024/NĐ-CP</t>
+          <t>42/2016/NĐ-CP</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=173412</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=141668</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2893,29 +2827,22 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>unanswerable_as_asked</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>Câu hỏi hỏi 'cơ quan chuyên môn về giao thông ở địa phương được gọi tên theo sở nào', nhưng khoản 2 không nói về sở; chỗ đổi là Bộ phải thống nhất trước khi mở tuyến xe buýt vào cảng hàng không (Bộ Giao thông vận tải → Bộ Xây dựng)</t>
-        </is>
-      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>vilextime:T4:provision:dcf457d0-3b96-11f1-b174-b5c1cf7b0c30:2026-08-10</t>
+          <t>vilextime:T4:provision:dcf457d0-3b96-11f1-b174-b5c1cf7b0c30:2026-08-09</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2925,12 +2852,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Khi Ủy ban nhân dân cấp tỉnh thực hiện nhiệm vụ quản lý vận tải đường bộ, cơ quan chuyên môn về giao thông ở địa phương được gọi tên theo sở nào?</t>
+          <t>Trước khi mở tuyến xe buýt đi đến hoặc xuất phát từ khu vực cảng hàng không, Ủy ban nhân dân cấp tỉnh phải thống nhất với bộ nào?</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2940,7 +2867,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2. Phối hợp với Ủy ban nhân dân cấp tỉnh có tuyến xe buýt đi qua để thống nhất thực hiện các nhiệm vụ nêu tại khoản 3 Điều 5 của Nghị định này. Thống nhất với Bộ Xây dựng trước khi mở tuyến xe buýt có điểm đầu hoặc điểm cuối nằm trong khu vực cảng hàng không.</t>
+          <t>2. Phối hợp với Ủy ban nhân dân cấp tỉnh có tuyến xe buýt đi qua để thống nhất thực hiện các nhiệm vụ nêu tại khoản 3 Điều 5 của Nghị định này. Thống nhất với Bộ Giao thông vận tải trước khi mở tuyến xe buýt có điểm đầu hoặc điểm cuối nằm trong khu vực cảng hàng không.</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2965,29 +2892,26 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>unanswerable_as_asked</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Câu hỏi hỏi 'cơ quan chuyên môn về giao thông ở địa phương được gọi tên theo sở nào', nhưng khoản 2 không nói về sở; chỗ đổi là Bộ phải thống nhất trước khi mở tuyến xe buýt vào cảng hàng không (Bộ Giao thông vận tải → Bộ Xây dựng)</t>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Khi Ủy ban nhân dân cấp tỉnh thực hiện nhiệm vụ quản lý vận tải đường bộ, cơ quan chuyên môn về giao thông ở địa phương được gọi tên theo sở nào?»; nhãn cũ khong_dat unanswerable_as_asked: Câu hỏi hỏi 'cơ quan chuyên môn về giao thông ở địa phương được gọi tên theo sở nào', nhưng khoản 2 không nói về sở; chỗ đổi là Bộ phải thống nhất trước khi mở tuyến xe buýt vào cảng hàng không (Bộ Giao thông vận tải → Bộ Xây dựng)). Câu hỏi hỏi bộ phải thống nhất, chạm chỗ đổi</t>
         </is>
       </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>vilextime:T4:provision:fc79fb04-2c7e-11f1-9a1a-67adfcf2b37c:2024-11-21</t>
+          <t>vilextime:T4:provision:dcf457d0-3b96-11f1-b174-b5c1cf7b0c30:2026-08-10</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2997,37 +2921,37 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Một tổ chức nhận văn bản thông báo kết quả đánh giá hồ sơ tuyển chọn nhiệm vụ của chương trình năng suất chất lượng thì văn bản đó do cơ quan nào ban hành?</t>
+          <t>Trước khi mở tuyến xe buýt đi đến hoặc xuất phát từ khu vực cảng hàng không, Ủy ban nhân dân cấp tỉnh phải thống nhất với bộ nào?</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Điều 19. Chuyên gia tư vấn độc lập đánh giá hồ sơ đăng ký tuyển chọn, giao trực tiếp thực hiện nhiệm vụ Việc đánh giá của chuyên gia tư vấn độc lập đối với hồ sơ đăng ký tuyển chọn, giao trực tiếp thực hiện nhiệm vụ được thực hiện theo quy định tại Điều 18, 19, 20 Chương IV Thông tư số 08/2017/TT-BKHCN. Áp dụng cụ thể đối với các nhiệm vụ thuộc Chương trình như sau:</t>
+          <t>Điều 73. Ủy ban nhân dân cấp tỉnh</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>6. Trong thời hạn 10 ngày kể từ ngày nhận được văn bản thông báo của tổng cục Tiêu chuẩn Đo lường Chất lượng theo quy định tại khoản 5 Điều này, tổ chức được kiến nghị chủ trì thực hiện nhiệm vụ hoàn thiện và gửi hồ sơ cho Tổng cục Tiêu chuẩn Đo lường Chất lượng.</t>
+          <t>2. Phối hợp với Ủy ban nhân dân cấp tỉnh có tuyến xe buýt đi qua để thống nhất thực hiện các nhiệm vụ nêu tại khoản 3 Điều 5 của Nghị định này. Thống nhất với Bộ Xây dựng trước khi mở tuyến xe buýt có điểm đầu hoặc điểm cuối nằm trong khu vực cảng hàng không.</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Khoản 6 Điều 19</t>
+          <t>Khoản 2 Điều 73</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>15/2022/TT-BKHCN</t>
+          <t>158/2024/NĐ-CP</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=160095</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=173412</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3037,29 +2961,26 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>group_mismatch</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Văn bản thông báo vẫn là của 'tổng cục Tiêu chuẩn Đo lường Chất lượng' ở cả hai mốc (chữ viết thường nên lần thay tên không chạm tới); chỗ đổi là nơi nhận hồ sơ (Tổng cục → Ủy ban), câu hỏi không hỏi</t>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Khi Ủy ban nhân dân cấp tỉnh thực hiện nhiệm vụ quản lý vận tải đường bộ, cơ quan chuyên môn về giao thông ở địa phương được gọi tên theo sở nào?»; nhãn cũ khong_dat unanswerable_as_asked: Câu hỏi hỏi 'cơ quan chuyên môn về giao thông ở địa phương được gọi tên theo sở nào', nhưng khoản 2 không nói về sở; chỗ đổi là Bộ phải thống nhất trước khi mở tuyến xe buýt vào cảng hàng không (Bộ Giao thông vận tải → Bộ Xây dựng)). Câu hỏi hỏi bộ phải thống nhất, chạm chỗ đổi</t>
         </is>
       </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>vilextime:T4:provision:fc79fb04-2c7e-11f1-9a1a-67adfcf2b37c:2024-11-22</t>
+          <t>vilextime:T4:provision:fc79fb04-2c7e-11f1-9a1a-67adfcf2b37c:2024-11-21</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3069,12 +2990,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Một tổ chức nhận văn bản thông báo kết quả đánh giá hồ sơ tuyển chọn nhiệm vụ của chương trình năng suất chất lượng thì văn bản đó do cơ quan nào ban hành?</t>
+          <t>Sau khi nhận văn bản thông báo kết quả đánh giá hồ sơ tuyển chọn nhiệm vụ của chương trình năng suất chất lượng, tổ chức được kiến nghị chủ trì phải hoàn thiện và gửi hồ sơ cho cơ quan nào trong thời hạn bao lâu?</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3084,7 +3005,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>6. Trong thời hạn 10 ngày kể từ ngày nhận được văn bản thông báo của tổng cục Tiêu chuẩn Đo lường Chất lượng theo quy định tại khoản 5 Điều này, tổ chức được kiến nghị chủ trì thực hiện nhiệm vụ hoàn thiện và gửi hồ sơ cho Ủy ban Tiêu chuẩn Đo lường Chất lượng Quốc gia.</t>
+          <t>6. Trong thời hạn 10 ngày kể từ ngày nhận được văn bản thông báo của tổng cục Tiêu chuẩn Đo lường Chất lượng theo quy định tại khoản 5 Điều này, tổ chức được kiến nghị chủ trì thực hiện nhiệm vụ hoàn thiện và gửi hồ sơ cho Tổng cục Tiêu chuẩn Đo lường Chất lượng.</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -3109,24 +3030,90 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>group_mismatch</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Văn bản thông báo vẫn là của 'tổng cục Tiêu chuẩn Đo lường Chất lượng' ở cả hai mốc (chữ viết thường nên lần thay tên không chạm tới); chỗ đổi là nơi nhận hồ sơ (Tổng cục → Ủy ban), câu hỏi không hỏi</t>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Một tổ chức nhận văn bản thông báo kết quả đánh giá hồ sơ tuyển chọn nhiệm vụ của chương trình năng suất chất lượng thì văn bản đó do cơ quan nào ban hành?»; nhãn cũ khong_dat group_mismatch: Văn bản thông báo vẫn là của 'tổng cục Tiêu chuẩn Đo lường Chất lượng' ở cả hai mốc (chữ viết thường nên lần thay tên không chạm tới); chỗ đổi là nơi nhận hồ sơ (Tổng cục → Ủy ban), câu hỏi không hỏi). Câu hỏi hỏi nơi nhận hồ sơ, chạm chỗ đổi</t>
         </is>
       </c>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>vilextime:T4:provision:fc79fb04-2c7e-11f1-9a1a-67adfcf2b37c:2024-11-22</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Sau khi nhận văn bản thông báo kết quả đánh giá hồ sơ tuyển chọn nhiệm vụ của chương trình năng suất chất lượng, tổ chức được kiến nghị chủ trì phải hoàn thiện và gửi hồ sơ cho cơ quan nào trong thời hạn bao lâu?</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2024-11-22</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Điều 19. Chuyên gia tư vấn độc lập đánh giá hồ sơ đăng ký tuyển chọn, giao trực tiếp thực hiện nhiệm vụ Việc đánh giá của chuyên gia tư vấn độc lập đối với hồ sơ đăng ký tuyển chọn, giao trực tiếp thực hiện nhiệm vụ được thực hiện theo quy định tại Điều 18, 19, 20 Chương IV Thông tư số 08/2017/TT-BKHCN. Áp dụng cụ thể đối với các nhiệm vụ thuộc Chương trình như sau:</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>6. Trong thời hạn 10 ngày kể từ ngày nhận được văn bản thông báo của tổng cục Tiêu chuẩn Đo lường Chất lượng theo quy định tại khoản 5 Điều này, tổ chức được kiến nghị chủ trì thực hiện nhiệm vụ hoàn thiện và gửi hồ sơ cho Ủy ban Tiêu chuẩn Đo lường Chất lượng Quốc gia.</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Khoản 6 Điều 19</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>15/2022/TT-BKHCN</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=160095</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Một tổ chức nhận văn bản thông báo kết quả đánh giá hồ sơ tuyển chọn nhiệm vụ của chương trình năng suất chất lượng thì văn bản đó do cơ quan nào ban hành?»; nhãn cũ khong_dat group_mismatch: Văn bản thông báo vẫn là của 'tổng cục Tiêu chuẩn Đo lường Chất lượng' ở cả hai mốc (chữ viết thường nên lần thay tên không chạm tới); chỗ đổi là nơi nhận hồ sơ (Tổng cục → Ủy ban), câu hỏi không hỏi). Câu hỏi hỏi nơi nhận hồ sơ, chạm chỗ đổi</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/review/audit_T4.xlsx
+++ b/data/review/audit_T4.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S39"/>
+  <dimension ref="A1:W65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,75 +439,95 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>also_asked_at</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>lead_in</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>answer</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>citation</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>law_id</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>source_url</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>amended_by</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>legal_markers</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>validity_flags</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
         <is>
           <t>labeler</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>verdict</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>reasons</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>meta_issues</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>evidence</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>fix</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>audit</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>auditor</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>audit_note</t>
         </is>
@@ -536,51 +556,71 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>2025-03-24 (giua_khoang)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>Điều 66. Quy hoạch sử dụng đất cấp huyện</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>4. Quận, thành phố, thị xã thuộc thành phố trực thuộc Trung ương, thành phố, thị xã thuộc tỉnh đã có quy hoạch chung hoặc quy hoạch phân khu được phê duyệt theo quy định của pháp luật về quy hoạch đô thị thì không phải lập quy hoạch sử dụng đất cấp huyện mà căn cứ vào quy hoạch chung hoặc quy hoạch phân khu và chỉ tiêu sử dụng đất đã được phân bổ từ quy hoạch sử dụng đất cấp tỉnh và các chỉ tiêu sử dụng đất của địa phương để lập kế hoạch sử dụng đất hằng năm cấp huyện.</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Khoản 4 Điều 66</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>31/2024/QH15</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=177815</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>claude-opus-5-5</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>dat</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+          <t>47/2024/QH15</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>actor_has_transitional</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>cap_huyen 2025-07-01 chờ; cap_huyen 2025-08-10 chờ; document_ended 2024-08-01 bao_dong_gia</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Trường hợp quận, thành phố thuộc thành phố trực thuộc trung ương đã có quy hoạch được phê duyệt, loại quy hoạch nào cho phép không phải lập quy hoạch sử dụng đất cấp huyện?»; nhãn cũ khong_dat group_mismatch: Loại quy hoạch (quy hoạch chung hoặc quy hoạch phân khu) như nhau ở hai mốc; chỉ đổi tên luật dẫn chiếu (quy hoạch đô thị → quy hoạch đô thị và nông thôn)). Câu hỏi hỏi pháp luật phê duyệt, chạm chỗ đổi tên luật</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Trường hợp quận, thành phố thuộc thành phố trực thuộc trung ương đã có quy hoạch được phê duyệt, loại quy hoạch nào cho phép không phải lập quy hoạch sử dụng đất cấp huyện?»; nhãn cũ khong_dat group_mismatch: Loại quy hoạch (quy hoạch chung hoặc quy hoạch phân khu) như nhau ở hai mốc; chỉ đổi tên luật dẫn chiếu (quy hoạch đô thị → quy hoạch đô thị và nông thôn)). Câu hỏi hỏi pháp luật phê duyệt, chạm chỗ đổi tên luật</t>
+        </is>
+      </c>
       <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -605,51 +645,71 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>2025-08-10 (giua_khoang)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>Điều 66. Quy hoạch sử dụng đất cấp huyện</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>4. Quận, thành phố, thị xã thuộc thành phố trực thuộc Trung ương, thành phố, thị xã thuộc tỉnh đã có quy hoạch chung hoặc quy hoạch phân khu được phê duyệt theo quy định của pháp luật về quy hoạch đô thị và nông thôn thì không phải lập quy hoạch sử dụng đất cấp huyện mà căn cứ vào quy hoạch chung hoặc quy hoạch phân khu và chỉ tiêu sử dụng đất đã được phân bổ từ quy hoạch sử dụng đất cấp tỉnh và các chỉ tiêu sử dụng đất của địa phương để lập kế hoạch sử dụng đất hằng năm cấp huyện.</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Khoản 4 Điều 66</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>31/2024/QH15</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=177815</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>claude-opus-5-5</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>dat</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+          <t>47/2024/QH15</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>actor_has_transitional</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>cap_huyen 2025-07-01 chờ; cap_huyen 2025-08-10 chờ; document_ended 2024-08-01 bao_dong_gia</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Trường hợp quận, thành phố thuộc thành phố trực thuộc trung ương đã có quy hoạch được phê duyệt, loại quy hoạch nào cho phép không phải lập quy hoạch sử dụng đất cấp huyện?»; nhãn cũ khong_dat group_mismatch: Loại quy hoạch (quy hoạch chung hoặc quy hoạch phân khu) như nhau ở hai mốc; chỉ đổi tên luật dẫn chiếu (quy hoạch đô thị → quy hoạch đô thị và nông thôn)). Câu hỏi hỏi pháp luật phê duyệt, chạm chỗ đổi tên luật</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Trường hợp quận, thành phố thuộc thành phố trực thuộc trung ương đã có quy hoạch được phê duyệt, loại quy hoạch nào cho phép không phải lập quy hoạch sử dụng đất cấp huyện?»; nhãn cũ khong_dat group_mismatch: Loại quy hoạch (quy hoạch chung hoặc quy hoạch phân khu) như nhau ở hai mốc; chỉ đổi tên luật dẫn chiếu (quy hoạch đô thị → quy hoạch đô thị và nông thôn)). Câu hỏi hỏi pháp luật phê duyệt, chạm chỗ đổi tên luật</t>
+        </is>
+      </c>
       <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -672,65 +732,73 @@
           <t>2021-03-14</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
         <is>
           <t>1. Đối tượng được xem xét cấp thẻ kiểm soát an ninh cảng hàng không, sân bay có giá trị sử dụng dài hạn bao gồm:</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>a) Cán bộ, nhân viên của các hãng hàng không, doanh nghiệp cảng hàng không, sân bay, doanh nghiệp cung cấp dịch vụ tại khu vực hạn chế của cảng hàng không, sân bay có hợp đồng lao động xác định thời hạn hoặc hợp đồng không xác định thời hạn theo quy định của pháp luật về lao động;</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Điểm a Khoản 1 Điều 14</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>13/2019/TT-BGTVT</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=135450</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>claude-opus-5-5</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>question_ambiguous</t>
-        </is>
-      </c>
+          <t>41/2020/TT-BGTVT</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>khong_dat</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>question_ambiguous</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
           <t>Điểm b (doanh nghiệp giao nhận hàng hóa, bưu gửi bằng đường hàng không) và điểm c (doanh nghiệp khảo sát, thi công, sửa chữa, bảo dưỡng tại cảng) cùng khoản cũng là doanh nghiệp có nhân viên được xem xét cấp thẻ dài hạn</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>b) Nhân viên của doanh nghiệp giao nhận hàng hóa, bưu gửi bằng đường hàng không;</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>loại lineage (question_ambiguous): Điểm b (doanh nghiệp giao nhận hàng hóa, bưu gửi bằng đường hàng không) và điểm c (doanh nghiệp khảo sát, thi công, sửa chữa, bảo dưỡng tại cảng) cùng khoản cũng là doanh nghiệp có nhân viên được xem xét cấp thẻ dài hạn</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -753,70 +821,78 @@
           <t>2021-03-15</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
         <is>
           <t>1. Đối tượng được xem xét cấp thẻ kiểm soát an ninh cảng hàng không, sân bay có giá trị sử dụng dài hạn bao gồm:</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>a) Cán bộ, nhân viên của các hãng hàng không, doanh nghiệp cảng hàng không, sân bay, doanh nghiệp cung cấp dịch vụ, du lịch tại khu vực hạn chế của cảng hàng không, sân bay có hợp đồng lao động xác định thời hạn hoặc hợp đồng không xác định thời hạn theo quy định của pháp luật về lao động;</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Điểm a Khoản 1 Điều 14</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>13/2019/TT-BGTVT</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=135450</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>claude-opus-5-5</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>question_ambiguous</t>
-        </is>
-      </c>
+          <t>41/2020/TT-BGTVT</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>khong_dat</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>question_ambiguous</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
           <t>Điểm b (doanh nghiệp giao nhận hàng hóa, bưu gửi bằng đường hàng không) và điểm c (doanh nghiệp khảo sát, thi công, sửa chữa, bảo dưỡng tại cảng) cùng khoản cũng là doanh nghiệp có nhân viên được xem xét cấp thẻ dài hạn</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>b) Nhân viên của doanh nghiệp giao nhận hàng hóa, bưu gửi bằng đường hàng không;</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>loại lineage (question_ambiguous): Điểm b (doanh nghiệp giao nhận hàng hóa, bưu gửi bằng đường hàng không) và điểm c (doanh nghiệp khảo sát, thi công, sửa chữa, bảo dưỡng tại cảng) cùng khoản cũng là doanh nghiệp có nhân viên được xem xét cấp thẻ dài hạn</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>vilextime:T4:provision:13f26650-2df0-11f1-aa8a-83f37d2cd5b7:2025-09-10</t>
+          <t>vilextime:T4:provision:0b910900-210a-11f1-b748-c1eb115306ea:2023-12-29</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -826,66 +902,78 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Trong lĩnh vực chào bán chứng khoán ra công chúng, sau khi Giấy chứng nhận đăng ký chào bán có hiệu lực thì tổ chức phát hành phải công bố những tài liệu nào?</t>
+          <t>Khi sắp xếp lại thị trường giao dịch cổ phiếu, chứng chỉ quỹ và chứng quyền, thời hạn chậm nhất để Sở Giao dịch Chứng khoán thành phố Hồ Chí Minh thống nhất tổ chức thị trường là khi nào?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2023-12-29</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Điều 41. Trình tự, thủ tục chào bán chứng khoán ra công chúng</t>
+          <t>2023-09-22 (giua_khoang)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>5. Trong thời hạn 07 ngày làm việc kể từ ngày Giấy chứng nhận đăng ký chào bán chứng khoán ra công chúng có hiệu lực, tổ chức phát hành, cổ đông đăng ký chào bán phải công bố Bản thông báo phát hành trên 01 tờ báo điện tử hoặc báo in trong 03 số liên tiếp theo quy định tại khoản 3 Điều 25 Luật Chứng khoán và công bố thông tin trên trang thông tin điện tử của tổ chức phát hành, cổ đông đăng ký chào bán là tổ chức (nếu có), Sở giao dịch chứng khoán. Bản cáo bạch chính thức phải được đồng thời đăng tải trên trang thông tin điện tử của tổ chức phát hành, cổ đông đăng ký chào bán là tổ chức (nếu có) và Sở giao dịch chứng khoán.</t>
+          <t>Điều 4. Sắp xếp lại thị trường giao dịch cổ phiếu, chứng chỉ quỹ và chứng quyền có bảo đảm</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Khoản 5 Điều 41</t>
+          <t>1. Chậm nhất đến hết ngày 30 tháng 6 năm 2025, Sở Giao dịch Chứng khoán thành phố Hồ Chí Minh thống nhất tổ chức thị trường giao dịch cổ phiếu, chứng chỉ quỹ và chứng quyền có bảo đảm niêm yết, thị trường giao dịch cổ phiếu của tổ chức đăng ký giao dịch theo quy định tại Luật Chứng khoán và các văn bản hướng dẫn thi hành.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>155/2020/NĐ-CP</t>
+          <t>Khoản 1 Điều 4</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=146467</t>
+          <t>57/2021/TT-BTC</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>claude-opus-5-5</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=151041</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>dat</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
+          <t>69/2023/TT-BTC</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>actor_has_transitional</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Tài liệu thêm ở mốc 2 chỉ áp cho tổ chức tài chính quốc tế chào bán trái phiếu; với tổ chức phát hành thông thường hai mốc như nhau — audit xem có coi là group_mismatch</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>vilextime:T4:provision:2e2bfeb0-2c5a-11f1-ae59-fb94f0483635:2025-05-02</t>
+          <t>vilextime:T4:provision:0b910900-210a-11f1-b748-c1eb115306ea:2023-12-30</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -895,62 +983,78 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Trường hợp Ủy ban nhân dân tỉnh có biển tổng hợp tình hình giao khu vực biển trên địa bàn, báo cáo phải gửi cho bộ nào?</t>
+          <t>Khi sắp xếp lại thị trường giao dịch cổ phiếu, chứng chỉ quỹ và chứng quyền, thời hạn chậm nhất để Sở Giao dịch Chứng khoán thành phố Hồ Chí Minh thống nhất tổ chức thị trường là khi nào?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2023-12-30</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Điều 40. Trách nhiệm của Ủy ban nhân dân cấp tỉnh có biển</t>
+          <t>2025-01-15 (giua_khoang)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>5. Tổng hợp, đánh giá tình hình giao, sử dụng khu vực biển trên địa bàn tỉnh; gửi báo cáo Bộ Nông nghiệp và Môi trường theo quy định trước ngày 15 tháng 01 hằng năm.</t>
+          <t>Điều 4. Sắp xếp lại thị trường giao dịch cổ phiếu, chứng chỉ quỹ và chứng quyền có bảo đảm</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Khoản 5 Điều 40</t>
+          <t>1. Chậm nhất đến hết ngày 31 tháng 12 năm 2026, Sở Giao dịch Chứng khoán thành phố Hồ Chí Minh thống nhất tổ chức thị trường giao dịch cổ phiếu, chứng chỉ quỹ và chứng quyền có bảo đảm niêm yết, thị trường giao dịch cổ phiếu của tổ chức đăng ký giao dịch theo quy định tại Luật Chứng khoán và các văn bản hướng dẫn thi hành.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>11/2021/NĐ-CP</t>
+          <t>Khoản 1 Điều 4</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=146676</t>
+          <t>57/2021/TT-BTC</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>claude-opus-5-5</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=151041</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>dat</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
+          <t>69/2023/TT-BTC</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>actor_has_transitional</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>vilextime:T4:provision:31904fe0-1f97-11f1-8e84-2dec611fd43c:2025-07-08</t>
+          <t>vilextime:T4:provision:0bb84010-210a-11f1-b4a7-7b33a09f6db3:2023-12-29</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -960,62 +1064,78 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Một túi ngoại giao gửi qua dịch vụ chuyển phát nhanh có dấu hiệu vi phạm chế độ ưu đãi, miễn trừ thì người đứng đầu cơ quan hải quan cấp nào có thẩm quyền quyết định kiểm tra?</t>
+          <t>Một tổ chức đã nộp hồ sơ niêm yết cổ phiếu tại Sở Giao dịch Chứng khoán Hà Nội nhưng chưa được chấp thuận thì hồ sơ được xử lý thế nào và mốc thời hạn nộp hồ sơ được xác định ra sao?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2023-12-29</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2. Túi ngoại giao, túi lãnh sự xuất khẩu, nhập khẩu gửi qua dịch vụ chuyển phát nhanh quốc tế:</t>
+          <t>2023-06-18 (giua_khoang)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>b) Khi có căn cứ để khẳng định túi ngoại giao, túi lãnh sự vi phạm chế độ ưu đãi, miễn trừ theo quy định của pháp luật, Tổng cục trưởng Tổng cục Hải quan quyết định việc xử lý theo quy định tại khoản 3 Điều 57 Luật Hải quan.</t>
+          <t>Điều 7. Xử lý hồ sơ đăng ký niêm yết, đăng ký giao dịch của tổ chức trong thời gian thực hiện kế hoạch chuyển chứng khoán niêm yết, đăng ký giao dịch</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Điểm b Khoản 2 Điều 7</t>
+          <t>2. Trường hợp tổ chức đã nộp hồ sơ đăng ký niêm yết cổ phiếu cho Sở Giao dịch Chứng khoán Hà Nội trước ngày 01 tháng 7 năm 2023 mà chưa được chấp thuận niêm yết, Sở Giao dịch Chứng khoán Hà Nội có trách nhiệm chuyển hồ sơ đăng ký niêm yết của tổ chức sang Sở Giao dịch Chứng khoán Thành phố Hồ Chí Minh trước ngày 06 tháng 7 năm 2023 để Sở Giao dịch Chứng khoán Thành phố Hồ Chí Minh tiếp tục xử lý hồ sơ đăng ký niêm yết của tổ chức theo quy định pháp luật.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>191/2015/TT-BTC</t>
+          <t>Khoản 2 Điều 7</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=110915</t>
+          <t>57/2021/TT-BTC</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>claude-opus-5-5</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=151041</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>dat</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
+          <t>69/2023/TT-BTC</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>actor_has_transitional</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>vilextime:T4:provision:3567d700-2474-11f1-b017-97c41f818c09:2026-01-25</t>
+          <t>vilextime:T4:provision:0bb84010-210a-11f1-b4a7-7b33a09f6db3:2023-12-30</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1025,62 +1145,78 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pháp luật về đo đạc và bản đồ quy định bộ nào công bố danh mục dự án khuyến khích tổ chức, cá nhân đầu tư xây dựng trạm định vị vệ tinh quốc gia?</t>
+          <t>Một tổ chức đã nộp hồ sơ niêm yết cổ phiếu tại Sở Giao dịch Chứng khoán Hà Nội nhưng chưa được chấp thuận thì hồ sơ được xử lý thế nào và mốc thời hạn nộp hồ sơ được xác định ra sao?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2023-12-30</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Điều 14. Tổ chức, cá nhân tham gia đầu tư, xây dựng, quản lý vận hành, bảo trì, khai thác công trình hạ tầng đo đạc</t>
+          <t>2025-08-23 (giua_khoang)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2. Bộ Nông nghiệp và Môi trường công bố danh mục dự án đầu tư khuyến khích tổ chức, cá nhân tham gia đầu tư xây dựng trạm định vị vệ tinh quốc gia, trạm định vị vệ tinh chuyên ngành thuộc phạm vi quản lý theo hình thức trực tiếp đầu tư hoặc đầu tư theo hình thức đối tác công tư; tổ chức triển khai thực hiện sau khi được phê duyệt theo quy định của pháp luật về đầu tư; lựa chọn nội dung về quản lý vận hành, bảo trì, khai thác công trình hạ tầng đo đạc khuyến khích các tổ chức, cá nhân tham gia đấu thầu thực hiện.</t>
+          <t>Điều 7. Xử lý hồ sơ đăng ký niêm yết, đăng ký giao dịch của tổ chức trong thời gian thực hiện kế hoạch chuyển chứng khoán niêm yết, đăng ký giao dịch</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Khoản 2 Điều 14</t>
+          <t>2. Trường hợp tổ chức đã nộp hồ sơ đăng ký niêm yết cổ phiếu cho Sở Giao dịch Chứng khoán Hà Nội trước ngày 01 tháng 7 năm 2025 mà chưa được chấp thuận niêm yết, Sở Giao dịch Chứng khoán Hà Nội có trách nhiệm chuyển hồ sơ đăng ký niêm yết của tổ chức sang Sở Giao dịch Chứng khoán thành phố Hồ Chí Minh trước ngày 08 tháng 7 năm 2025 để Sở Giao dịch Chứng khoán thành phố Hồ Chí Minh tiếp tục xử lý hồ sơ đăng ký niêm yết của tổ chức theo quy định pháp luật.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>27/2019/NĐ-CP</t>
+          <t>Khoản 2 Điều 7</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=134555</t>
+          <t>57/2021/TT-BTC</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>claude-opus-5-5</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=151041</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>dat</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
+          <t>69/2023/TT-BTC</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>actor_has_transitional</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>vilextime:T4:provision:3570fec0-2474-11f1-9738-f31dbb552ae2:2026-01-24</t>
+          <t>vilextime:T4:provision:13f26650-2df0-11f1-aa8a-83f37d2cd5b7:2025-09-10</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1090,66 +1226,82 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Khi di dời trạm định vị vệ tinh quốc gia, Ủy ban nhân dân cấp tỉnh phối hợp với bộ nào để tổ chức việc di dời?</t>
+          <t>Trong lĩnh vực chào bán chứng khoán ra công chúng, sau khi Giấy chứng nhận đăng ký chào bán có hiệu lực thì tổ chức phát hành phải công bố những tài liệu nào?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>7. Việc di dời trạm định vị vệ tinh thực hiện theo quy định sau đây:</t>
+          <t>2023-04-25 (giua_khoang)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>d) Ủy ban nhân dân cấp tỉnh phối hợp với Bộ Tài nguyên và Môi trường thông qua cơ quan quản lý chuyên ngành về đo đạc và bản đồ thuộc Bộ Tài nguyên và Môi trường tổ chức việc di dời trạm định vị vệ tinh quốc gia;</t>
+          <t>Điều 41. Trình tự, thủ tục chào bán chứng khoán ra công chúng</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Điểm d Khoản 7 Điều 17</t>
+          <t>5. Trong thời hạn 07 ngày làm việc kể từ ngày Giấy chứng nhận đăng ký chào bán chứng khoán ra công chúng có hiệu lực, tổ chức phát hành, cổ đông đăng ký chào bán phải công bố Bản thông báo phát hành trên 01 tờ báo điện tử hoặc báo in trong 03 số liên tiếp theo quy định tại khoản 3 Điều 25 Luật Chứng khoán và công bố thông tin trên trang thông tin điện tử của tổ chức phát hành, cổ đông đăng ký chào bán là tổ chức (nếu có), Sở giao dịch chứng khoán. Bản cáo bạch chính thức phải được đồng thời đăng tải trên trang thông tin điện tử của tổ chức phát hành, cổ đông đăng ký chào bán là tổ chức (nếu có) và Sở giao dịch chứng khoán.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>27/2019/NĐ-CP</t>
+          <t>Khoản 5 Điều 41</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=134555</t>
+          <t>155/2020/NĐ-CP</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>claude-opus-5-5</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=146467</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>dat</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
+          <t>245/2025/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>actor_has_transitional</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Theo quy định về di dời trạm định vị vệ tinh, Ủy ban nhân dân cấp tỉnh phối hợp với bộ nào để thực hiện?»; nhãn cũ khong_dat question_ambiguous: Câu hỏi không nêu trạm quốc gia; điểm đ cùng khoản quy định Ủy ban nhân dân cấp tỉnh phối hợp với bộ, cơ quan ngang bộ, cơ quan thuộc Chính phủ di dời trạm định vị vệ tinh chuyên ngành). Đã nêu trạm quốc gia, loại điểm đ</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr"/>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Tài liệu thêm ở mốc 2 chỉ áp cho tổ chức tài chính quốc tế chào bán trái phiếu; với tổ chức phát hành thông thường hai mốc như nhau — audit xem có coi là group_mismatch</t>
+        </is>
+      </c>
       <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>vilextime:T4:provision:3570fec0-2474-11f1-9738-f31dbb552ae2:2026-01-25</t>
+          <t>vilextime:T4:provision:13f26650-2df0-11f1-aa8a-83f37d2cd5b7:2025-09-11</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1159,66 +1311,82 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Khi di dời trạm định vị vệ tinh quốc gia, Ủy ban nhân dân cấp tỉnh phối hợp với bộ nào để tổ chức việc di dời?</t>
+          <t>Trong lĩnh vực chào bán chứng khoán ra công chúng, sau khi Giấy chứng nhận đăng ký chào bán có hiệu lực thì tổ chức phát hành phải công bố những tài liệu nào?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>7. Việc di dời trạm định vị vệ tinh thực hiện theo quy định sau đây:</t>
+          <t>2026-04-18 (giua_khoang)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>d) Ủy ban nhân dân cấp tỉnh phối hợp với Bộ Nông nghiệp và Môi trường thông qua cơ quan quản lý chuyên ngành về đo đạc và bản đồ thuộc Bộ Nông nghiệp và Môi trường tổ chức việc di dời trạm định vị vệ tinh quốc gia;</t>
+          <t>Điều 41. Trình tự, thủ tục chào bán chứng khoán ra công chúng</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Điểm d Khoản 7 Điều 17</t>
+          <t>5. Trong thời hạn 07 ngày làm việc kể từ ngày Giấy chứng nhận đăng ký chào bán chứng khoán ra công chúng có hiệu lực, tổ chức phát hành, cổ đông đăng ký chào bán phải công bố Bản thông báo phát hành trên 01 tờ báo điện tử hoặc báo in trong 03 số liên tiếp theo quy định tại khoản 3 Điều 25 Luật Chứng khoán và công bố thông tin trên trang thông tin điện tử của tổ chức phát hành, cổ đông đăng ký chào bán là tổ chức (nếu có), Sở giao dịch chứng khoán. Bản cáo bạch chính thức, Bản công bố thông tin chính thức (đối với trường hợp chào bán trái phiếu ra công chúng tại Việt Nam của tổ chức tài chính quốc tế) phải được đồng thời đăng tải trên trang thông tin điện tử của tổ chức phát hành, cổ đông đăng ký chào bán là tổ chức (nếu có) và Sở giao dịch chứng khoán.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>27/2019/NĐ-CP</t>
+          <t>Khoản 5 Điều 41</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=134555</t>
+          <t>155/2020/NĐ-CP</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>claude-opus-5-5</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=146467</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>dat</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
+          <t>245/2025/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>actor_has_transitional</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Theo quy định về di dời trạm định vị vệ tinh, Ủy ban nhân dân cấp tỉnh phối hợp với bộ nào để thực hiện?»; nhãn cũ khong_dat question_ambiguous: Câu hỏi không nêu trạm quốc gia; điểm đ cùng khoản quy định Ủy ban nhân dân cấp tỉnh phối hợp với bộ, cơ quan ngang bộ, cơ quan thuộc Chính phủ di dời trạm định vị vệ tinh chuyên ngành). Đã nêu trạm quốc gia, loại điểm đ</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr"/>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Tài liệu thêm ở mốc 2 chỉ áp cho tổ chức tài chính quốc tế chào bán trái phiếu; với tổ chức phát hành thông thường hai mốc như nhau — audit xem có coi là group_mismatch</t>
+        </is>
+      </c>
       <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>vilextime:T4:provision:35ca5850-2d46-11f1-8661-2356875ccd95:2025-07-20</t>
+          <t>vilextime:T4:provision:2e2bfeb0-2c5a-11f1-ae59-fb94f0483635:2025-05-02</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1228,66 +1396,74 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Khi có sĩ quan dự bị vắng mặt tại nơi cư trú, Ban Chỉ huy quân sự cấp xã phải tổng hợp báo cáo lên cơ quan quân sự nào và vào thời gian nào?</t>
+          <t>Trường hợp Ủy ban nhân dân tỉnh có biển tổng hợp tình hình giao khu vực biển trên địa bàn, báo cáo phải gửi cho bộ nào?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>4. Đăng ký vắng mặt</t>
+          <t>2025-11-06 (giua_khoang)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>a) Sĩ quan dự bị khi vắng mặt tại nơi cư trú hoặc nơi đang lao động, học tập, làm việc: Vắng mặt từ 30 ngày trở lên, sĩ quan dự bị phải báo cáo Ban Chỉ huy quân sự cấp xã, hoặc cơ quan, tổ chức nơi đang lao động, học tập, làm việc. Hằng tháng, nếu có sĩ quan dự bị vắng mặt, Ban Chỉ huy quân sự cấp xã, Ban Chỉ huy quân sự cơ quan, tổ chức tổng hợp báo cáo Ban Chỉ huy quân sự cấp huyện; Sĩ quan dự bị đã sắp xếp, bổ nhiệm vào đơn vị dự bị động viên vắng mặt từ 03 tháng trở lên, Ban Chỉ huy quân sự cấp huyện phải thông báo cho đơn vị nhận nguồn sĩ quan dự bị biết; khi có lệnh tổng động viên, hoặc động viên cục bộ, sĩ quan dự bị phải trở về ngay nơi cư trú, hoặc nơi đang lao động, học tập, làm việc để sẵn sàng nhận nhiệm vụ.</t>
+          <t>Điều 40. Trách nhiệm của Ủy ban nhân dân cấp tỉnh có biển</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Điểm a Khoản 4 Điều 10</t>
+          <t>5. Tổng hợp, đánh giá tình hình giao, sử dụng khu vực biển trên địa bàn tỉnh; gửi báo cáo Bộ Nông nghiệp và Môi trường theo quy định trước ngày 15 tháng 01 hằng năm.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>78/2020/NĐ-CP</t>
+          <t>Khoản 5 Điều 40</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=142838</t>
+          <t>11/2021/NĐ-CP</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>claude-opus-5-5</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=146676</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>dat</t>
+          <t>65/2025/NĐ-CP</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Khi sĩ quan dự bị vắng mặt tại nơi cư trú từ 30 ngày trở lên, người đó phải báo cáo cho cơ quan quân sự cấp nào và theo thời gian nào?»; nhãn cũ khong_dat group_mismatch: Người vắng mặt báo cáo Ban Chỉ huy quân sự cấp xã (hoặc nơi làm việc) ở cả hai mốc; chỗ đổi là việc Ban Chỉ huy quân sự cấp xã tổng hợp báo cáo lên cấp huyện → cấp tỉnh, từ ngày 25 đến 30 hằng tháng). Câu hỏi hỏi nơi nhận và thời gian báo cáo tổng hợp, chạm chỗ đổi</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr"/>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>vilextime:T4:provision:35ca5850-2d46-11f1-8661-2356875ccd95:2025-07-21</t>
+          <t>vilextime:T4:provision:31904fe0-1f97-11f1-8e84-2dec611fd43c:2025-07-08</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1297,66 +1473,74 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Khi có sĩ quan dự bị vắng mặt tại nơi cư trú, Ban Chỉ huy quân sự cấp xã phải tổng hợp báo cáo lên cơ quan quân sự nào và vào thời gian nào?</t>
+          <t>Một túi ngoại giao gửi qua dịch vụ chuyển phát nhanh có dấu hiệu vi phạm chế độ ưu đãi, miễn trừ thì người đứng đầu cơ quan hải quan cấp nào có thẩm quyền quyết định kiểm tra?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4. Đăng ký vắng mặt</t>
+          <t>2022-04-18 (giua_khoang)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>a) Sĩ quan dự bị khi vắng mặt tại nơi thường trú hoặc nơi đang lao động, học tập, làm việc Vắng mặt từ 30 ngày trở lên, sĩ quan dự bị phải báo cáo Ban Chỉ huy quân sự cấp xã, hoặc cơ quan, tổ chức nơi đang lao động, học tập, làm việc. Từ ngày 25 đến ngày 30 hằng tháng, nếu có sĩ quan dự bị vắng mặt, Ban Chỉ huy quân sự cấp xã, Ban Chỉ huy quân sự cơ quan, tổ chức tổng hợp báo cáo Bộ Chỉ huy quân sự cấp tỉnh; Sĩ quan dự bị đã sắp xếp, bổ nhiệm vào đơn vị dự bị động viên vắng mặt từ 03 tháng trở lên, Ban Chỉ huy quân sự cấp xã phải thông báo cho đơn vị nhận nguồn sĩ quan dự bị biết; khi có lệnh tổng động viên, hoặc động viên cục bộ, sĩ quan dự bị phải trở về ngay nơi thường trú hoặc nơi đang lao động, học tập, làm việc để sẵn sàng nhận nhiệm vụ;</t>
+          <t>2. Túi ngoại giao, túi lãnh sự xuất khẩu, nhập khẩu gửi qua dịch vụ chuyển phát nhanh quốc tế:</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Điểm a Khoản 4 Điều 10</t>
+          <t>b) Khi có căn cứ để khẳng định túi ngoại giao, túi lãnh sự vi phạm chế độ ưu đãi, miễn trừ theo quy định của pháp luật, Tổng cục trưởng Tổng cục Hải quan quyết định việc xử lý theo quy định tại khoản 3 Điều 57 Luật Hải quan.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>78/2020/NĐ-CP</t>
+          <t>Điểm b Khoản 2 Điều 7</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=142838</t>
+          <t>191/2015/TT-BTC</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>claude-opus-5-5</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=110915</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>dat</t>
+          <t>29/2025/TT-BTC</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Khi sĩ quan dự bị vắng mặt tại nơi cư trú từ 30 ngày trở lên, người đó phải báo cáo cho cơ quan quân sự cấp nào và theo thời gian nào?»; nhãn cũ khong_dat group_mismatch: Người vắng mặt báo cáo Ban Chỉ huy quân sự cấp xã (hoặc nơi làm việc) ở cả hai mốc; chỗ đổi là việc Ban Chỉ huy quân sự cấp xã tổng hợp báo cáo lên cấp huyện → cấp tỉnh, từ ngày 25 đến 30 hằng tháng). Câu hỏi hỏi nơi nhận và thời gian báo cáo tổng hợp, chạm chỗ đổi</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr"/>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>vilextime:T4:provision:3b4128da-2d47-11f1-98ce-1bf21bf5f6be:2021-07-15</t>
+          <t>vilextime:T4:provision:3567d700-2474-11f1-b017-97c41f818c09:2026-01-25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1366,62 +1550,74 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Việc đánh giá hồ sơ lựa chọn luật sư ký hợp đồng trợ giúp pháp lý được xác định ra sao về thời hạn hoàn thành và thời gian được kéo dài?</t>
+          <t>Pháp luật về đo đạc và bản đồ quy định bộ nào công bố danh mục dự án khuyến khích tổ chức, cá nhân đầu tư xây dựng trạm định vị vệ tinh quốc gia?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2021-07-15</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Điều 7. Đánh giá hồ sơ và ký hợp đồng với luật sư</t>
+          <t>2026-04-10 (giua_khoang)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1. Trong thời hạn 10 ngày kể từ ngày hết hạn nộp hồ sơ, Tổ đánh giá luật sư phải hoàn thành việc đánh giá. Trường hợp cần thiết, có thể kéo dài thời gian đánh giá nhưng không quá 03 ngày làm việc.</t>
+          <t>Điều 14. Tổ chức, cá nhân tham gia đầu tư, xây dựng, quản lý vận hành, bảo trì, khai thác công trình hạ tầng đo đạc</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Khoản 1 Điều 7</t>
+          <t>2. Bộ Nông nghiệp và Môi trường công bố danh mục dự án đầu tư khuyến khích tổ chức, cá nhân tham gia đầu tư xây dựng trạm định vị vệ tinh quốc gia, trạm định vị vệ tinh chuyên ngành thuộc phạm vi quản lý theo hình thức trực tiếp đầu tư hoặc đầu tư theo hình thức đối tác công tư; tổ chức triển khai thực hiện sau khi được phê duyệt theo quy định của pháp luật về đầu tư; lựa chọn nội dung về quản lý vận hành, bảo trì, khai thác công trình hạ tầng đo đạc khuyến khích các tổ chức, cá nhân tham gia đấu thầu thực hiện.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>08/2017/TT-BTP</t>
+          <t>Khoản 2 Điều 14</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=127076</t>
+          <t>27/2019/NĐ-CP</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>claude-opus-5-5</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=134555</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>dat</t>
+          <t>39/2026/NĐ-CP</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>vilextime:T4:provision:524dc410-2857-11f1-b228-d7f831690dec:2026-01-08</t>
+          <t>vilextime:T4:provision:3570fec0-2474-11f1-9738-f31dbb552ae2:2026-01-24</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1431,62 +1627,78 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Khi vi phạm quy định về đăng ký, lưu ký, bù trừ chứng khoán bị phạt tiền từ 400.000.000 đồng đến 500.000.000 đồng, những tổ chức nào là đối tượng bị xử phạt?</t>
+          <t>Khi di dời trạm định vị vệ tinh quốc gia, Ủy ban nhân dân cấp tỉnh phối hợp với bộ nào để tổ chức việc di dời?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Điều 39. Vi phạm quy định về đăng ký, lưu ký, bù trừ và thanh toán chứng khoán</t>
+          <t>2021-05-02 (giua_khoang)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>5. Phạt tiền từ 400.000.000 đồng đến 500.000.000 đồng đối với Tổng công ty lưu ký và bù trừ chứng khoán Việt Nam, thành viên lưu ký, thành viên bù trừ và phạt tiền từ 200.000.000 đồng đến 250.000.000 đồng đối với nhân viên của thành viên lưu ký, thành viên bù trừ thực hiện hành vi sửa chữa, làm thất lạc chúng từ trong thanh toán, chuyển giao quyền sở hữu chứng khoán.</t>
+          <t>7. Việc di dời trạm định vị vệ tinh thực hiện theo quy định sau đây:</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Khoản 5 Điều 39</t>
+          <t>d) Ủy ban nhân dân cấp tỉnh phối hợp với Bộ Tài nguyên và Môi trường thông qua cơ quan quản lý chuyên ngành về đo đạc và bản đồ thuộc Bộ Tài nguyên và Môi trường tổ chức việc di dời trạm định vị vệ tinh quốc gia;</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>156/2020/NĐ-CP</t>
+          <t>Điểm d Khoản 7 Điều 17</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=146468</t>
+          <t>27/2019/NĐ-CP</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>claude-opus-5-5</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=134555</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>dat</t>
+          <t>39/2026/NĐ-CP</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Theo quy định về di dời trạm định vị vệ tinh, Ủy ban nhân dân cấp tỉnh phối hợp với bộ nào để thực hiện?»; nhãn cũ khong_dat question_ambiguous: Câu hỏi không nêu trạm quốc gia; điểm đ cùng khoản quy định Ủy ban nhân dân cấp tỉnh phối hợp với bộ, cơ quan ngang bộ, cơ quan thuộc Chính phủ di dời trạm định vị vệ tinh chuyên ngành). Đã nêu trạm quốc gia, loại điểm đ</t>
+        </is>
+      </c>
       <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>vilextime:T4:provision:52a33850-3171-11f1-a40f-5b548501b65a:2025-05-02</t>
+          <t>vilextime:T4:provision:3570fec0-2474-11f1-9738-f31dbb552ae2:2026-01-25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1496,62 +1708,78 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Khi xây dựng dự thảo chương trình trọng điểm điều tra tài nguyên, môi trường biển, bộ nào tổng hợp, rà soát các dự án, đề án được đề xuất?</t>
+          <t>Khi di dời trạm định vị vệ tinh quốc gia, Ủy ban nhân dân cấp tỉnh phối hợp với bộ nào để tổ chức việc di dời?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Điều 24. Tổng hợp, rà soát các dự án, đề án, nhiệm vụ và xây dựng dự thảo chương trình</t>
+          <t>2026-03-31 (giua_khoang)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1. Bộ Nông nghiệp và Môi trường tổng hợp, rà soát dự án, đề án, nhiệm vụ đưa vào chương trình theo nguyên tắc, căn cứ và yêu cầu quy định tại Điều 20 và Điều 21 Nghị định này.</t>
+          <t>7. Việc di dời trạm định vị vệ tinh thực hiện theo quy định sau đây:</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Khoản 1 Điều 24</t>
+          <t>d) Ủy ban nhân dân cấp tỉnh phối hợp với Bộ Nông nghiệp và Môi trường thông qua cơ quan quản lý chuyên ngành về đo đạc và bản đồ thuộc Bộ Nông nghiệp và Môi trường tổ chức việc di dời trạm định vị vệ tinh quốc gia;</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>40/2016/NĐ-CP</t>
+          <t>Điểm d Khoản 7 Điều 17</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=110836</t>
+          <t>27/2019/NĐ-CP</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>claude-opus-5-5</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=134555</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>dat</t>
+          <t>39/2026/NĐ-CP</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Theo quy định về di dời trạm định vị vệ tinh, Ủy ban nhân dân cấp tỉnh phối hợp với bộ nào để thực hiện?»; nhãn cũ khong_dat question_ambiguous: Câu hỏi không nêu trạm quốc gia; điểm đ cùng khoản quy định Ủy ban nhân dân cấp tỉnh phối hợp với bộ, cơ quan ngang bộ, cơ quan thuộc Chính phủ di dời trạm định vị vệ tinh chuyên ngành). Đã nêu trạm quốc gia, loại điểm đ</t>
+        </is>
+      </c>
       <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>vilextime:T4:provision:55ac5bec-df4d-11f0-b470-a3516d537d9d#k1#b:2023-02-28</t>
+          <t>vilextime:T4:provision:35ca5850-2d46-11f1-8661-2356875ccd95:2025-07-20</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1561,62 +1789,82 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Theo quy định về thay đổi tên của tổ chức tín dụng là hợp tác xã, hồ sơ phải có văn bản nào của Đại hội thành viên?</t>
+          <t>Khi có sĩ quan dự bị vắng mặt tại nơi cư trú, Ban Chỉ huy quân sự cấp xã phải tổng hợp báo cáo lên cơ quan quân sự nào và vào thời gian nào?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2023-02-28</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1. Hồ sơ đề nghị gồm:</t>
+          <t>2024-09-01 (giua_khoang)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>b) Quyết định của Đại hội thành viên thông qua việc thay đổi tên.</t>
+          <t>4. Đăng ký vắng mặt</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Điểm b Khoản 1 Điều 5</t>
+          <t>a) Sĩ quan dự bị khi vắng mặt tại nơi cư trú hoặc nơi đang lao động, học tập, làm việc: Vắng mặt từ 30 ngày trở lên, sĩ quan dự bị phải báo cáo Ban Chỉ huy quân sự cấp xã, hoặc cơ quan, tổ chức nơi đang lao động, học tập, làm việc. Hằng tháng, nếu có sĩ quan dự bị vắng mặt, Ban Chỉ huy quân sự cấp xã, Ban Chỉ huy quân sự cơ quan, tổ chức tổng hợp báo cáo Ban Chỉ huy quân sự cấp huyện; Sĩ quan dự bị đã sắp xếp, bổ nhiệm vào đơn vị dự bị động viên vắng mặt từ 03 tháng trở lên, Ban Chỉ huy quân sự cấp huyện phải thông báo cho đơn vị nhận nguồn sĩ quan dự bị biết; khi có lệnh tổng động viên, hoặc động viên cục bộ, sĩ quan dự bị phải trở về ngay nơi cư trú, hoặc nơi đang lao động, học tập, làm việc để sẵn sàng nhận nhiệm vụ.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>05/2018/TT-NHNN</t>
+          <t>Điểm a Khoản 4 Điều 10</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=128193</t>
+          <t>78/2020/NĐ-CP</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>claude-opus-5-5</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=142838</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>dat</t>
+          <t>209/2025/NĐ-CP</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>cap_huyen 2025-07-20 chờ</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Khi sĩ quan dự bị vắng mặt tại nơi cư trú từ 30 ngày trở lên, người đó phải báo cáo cho cơ quan quân sự cấp nào và theo thời gian nào?»; nhãn cũ khong_dat group_mismatch: Người vắng mặt báo cáo Ban Chỉ huy quân sự cấp xã (hoặc nơi làm việc) ở cả hai mốc; chỗ đổi là việc Ban Chỉ huy quân sự cấp xã tổng hợp báo cáo lên cấp huyện → cấp tỉnh, từ ngày 25 đến 30 hằng tháng). Câu hỏi hỏi nơi nhận và thời gian báo cáo tổng hợp, chạm chỗ đổi</t>
+        </is>
+      </c>
       <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>vilextime:T4:provision:5cc79b52-ec41-11f0-95e4-0f1dfe7bb184#k2#b:2015-06-30</t>
+          <t>vilextime:T4:provision:35ca5850-2d46-11f1-8661-2356875ccd95:2025-07-21</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1626,66 +1874,82 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Những người nào được cấp Giấy chứng nhận vùng hoạt động hoa tiêu hàng hải tại một vùng hoạt động và tuyến dẫn tàu căn cứ vào kinh nghiệm đã có tại vùng, tuyến đó?</t>
+          <t>Khi có sĩ quan dự bị vắng mặt tại nơi cư trú, Ban Chỉ huy quân sự cấp xã phải tổng hợp báo cáo lên cơ quan quân sự nào và vào thời gian nào?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2015-06-30</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2. Giấy chứng nhận vùng hoạt động hoa tiêu hàng hải</t>
+          <t>2026-04-05 (giua_khoang)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>b) Hoa tiêu hàng hải đã qua thực tập dẫn tàu ở vùng hoạt động và tuyến dẫn tàu nào thì được cấp GCNVHĐHTHH tại vùng hoạt động và tuyến dẫn tàu đó.</t>
+          <t>4. Đăng ký vắng mặt</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Điểm b Khoản 2 Điều 2</t>
+          <t>a) Sĩ quan dự bị khi vắng mặt tại nơi thường trú hoặc nơi đang lao động, học tập, làm việc Vắng mặt từ 30 ngày trở lên, sĩ quan dự bị phải báo cáo Ban Chỉ huy quân sự cấp xã, hoặc cơ quan, tổ chức nơi đang lao động, học tập, làm việc. Từ ngày 25 đến ngày 30 hằng tháng, nếu có sĩ quan dự bị vắng mặt, Ban Chỉ huy quân sự cấp xã, Ban Chỉ huy quân sự cơ quan, tổ chức tổng hợp báo cáo Bộ Chỉ huy quân sự cấp tỉnh; Sĩ quan dự bị đã sắp xếp, bổ nhiệm vào đơn vị dự bị động viên vắng mặt từ 03 tháng trở lên, Ban Chỉ huy quân sự cấp xã phải thông báo cho đơn vị nhận nguồn sĩ quan dự bị biết; khi có lệnh tổng động viên, hoặc động viên cục bộ, sĩ quan dự bị phải trở về ngay nơi thường trú hoặc nơi đang lao động, học tập, làm việc để sẵn sàng nhận nhiệm vụ;</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>36/2013/TT-BGTVT</t>
+          <t>Điểm a Khoản 4 Điều 10</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=37793</t>
+          <t>78/2020/NĐ-CP</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>claude-opus-5-5</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=142838</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>dat</t>
+          <t>209/2025/NĐ-CP</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>cap_huyen 2025-07-20 chờ</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Trường hợp cấp Giấy chứng nhận vùng hoạt động hoa tiêu hàng hải cho một vùng và tuyến dẫn tàu cụ thể, người được cấp phải đáp ứng điều kiện gì về thực tập dẫn tàu?»; nhãn cũ khong_dat group_mismatch: Với hoa tiêu, điều kiện thực tập dẫn tàu như nhau ở hai mốc; chỗ đổi thêm trường hợp thuyền trưởng đã dẫn tàu, câu hỏi không hỏi). Câu hỏi hỏi những người được cấp theo kinh nghiệm, chạm chỗ thêm thuyền trưởng</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr"/>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Khi sĩ quan dự bị vắng mặt tại nơi cư trú từ 30 ngày trở lên, người đó phải báo cáo cho cơ quan quân sự cấp nào và theo thời gian nào?»; nhãn cũ khong_dat group_mismatch: Người vắng mặt báo cáo Ban Chỉ huy quân sự cấp xã (hoặc nơi làm việc) ở cả hai mốc; chỗ đổi là việc Ban Chỉ huy quân sự cấp xã tổng hợp báo cáo lên cấp huyện → cấp tỉnh, từ ngày 25 đến 30 hằng tháng). Câu hỏi hỏi nơi nhận và thời gian báo cáo tổng hợp, chạm chỗ đổi</t>
+        </is>
+      </c>
       <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>vilextime:T4:provision:5cc79b52-ec41-11f0-95e4-0f1dfe7bb184#k2#b:2015-07-01</t>
+          <t>vilextime:T4:provision:39285060-2d46-11f1-9609-c70b8a86e128:2024-11-21</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1695,66 +1959,78 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Những người nào được cấp Giấy chứng nhận vùng hoạt động hoa tiêu hàng hải tại một vùng hoạt động và tuyến dẫn tàu căn cứ vào kinh nghiệm đã có tại vùng, tuyến đó?</t>
+          <t>Theo quy định về đo lường, chất lượng trong kinh doanh khí, cơ quan nào thuộc Bộ Khoa học và Công nghệ tổ chức triển khai và báo cáo Bộ?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2015-07-01</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2. Giấy chứng nhận vùng hoạt động hoa tiêu hàng hải</t>
+          <t>2023-05-01 (giua_khoang)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>b) Hoa tiêu hàng hải đã qua thực tập dẫn tàu, thuyền trưởng đã dẫn tàu ở vùng hoạt động và tuyến dẫn tàu nào thì được cấp GCNVHĐHTHH tại vùng hoạt động và tuyến dẫn tàu đó.</t>
+          <t>1. Bộ Khoa học và Công nghệ:</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Điểm b Khoản 2 Điều 2</t>
+          <t>h) Tổng cục Tiêu chuẩn Đo lường Chất lượng có trách nhiệm tổ chức triển khai thực hiện các điểm a, b, c, d, đ, e, g khoản này và báo cáo Bộ Khoa học và Công nghệ về kết quả triển khai thực hiện theo quy định về báo cáo định kỳ hoặc yêu cầu báo cáo đột xuất của Bộ Khoa học và Công nghệ.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>36/2013/TT-BGTVT</t>
+          <t>Điểm h Khoản 1 Điều 21</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=37793</t>
+          <t>20/2019/TT-BKHCN</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>claude-opus-5-5</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=142713</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>dat</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
+          <t>07/2024/TT-BKHCN</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>actor_has_transitional</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Trường hợp cấp Giấy chứng nhận vùng hoạt động hoa tiêu hàng hải cho một vùng và tuyến dẫn tàu cụ thể, người được cấp phải đáp ứng điều kiện gì về thực tập dẫn tàu?»; nhãn cũ khong_dat group_mismatch: Với hoa tiêu, điều kiện thực tập dẫn tàu như nhau ở hai mốc; chỗ đổi thêm trường hợp thuyền trưởng đã dẫn tàu, câu hỏi không hỏi). Câu hỏi hỏi những người được cấp theo kinh nghiệm, chạm chỗ thêm thuyền trưởng</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr"/>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>vilextime:T4:provision:683008bc-eb7e-11f0-8c9f-11c2354deb20:2023-09-17</t>
+          <t>vilextime:T4:provision:39285060-2d46-11f1-9609-c70b8a86e128:2024-11-22</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1764,66 +2040,78 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Văn bằng, chứng chỉ do nước ngoài cấp trong hồ sơ dự tuyển của người lao động Việt Nam làm việc cho tổ chức nước ngoài phải được dịch ra tiếng Việt và xác nhận bản dịch theo hình thức nào?</t>
+          <t>Theo quy định về đo lường, chất lượng trong kinh doanh khí, cơ quan nào thuộc Bộ Khoa học và Công nghệ tổ chức triển khai và báo cáo Bộ?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Điều 23. Hồ Sơ đăng ký dự tuyển của người lao động Việt Nam</t>
+          <t>2025-07-28 (giua_khoang)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>4. Bản sao có chứng thực văn bằng, chứng chỉ về trình độ chuyên môn kỹ thuật, nghiệp vụ, ngoại ngữ liên quan đến công việc mà người lao động đăng ký dự tuyển. Nếu của nước ngoài thì phải được hợp pháp hóa lãnh sự, trừ trường hợp được miễn hợp pháp hỏa lãnh sự theo điều ước quốc tế mà nước Cộng hòa xã hội chủ nghĩa Việt Nam và nước ngoài liên quan đều là thành viên hoặc theo nguyên tắc có đi có lại hoặc theo quy định của pháp luật; dịch ra tiếng Việt và chứng thực theo quy định của pháp luật Việt Nam.</t>
+          <t>1. Bộ Khoa học và Công nghệ:</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Khoản 4 Điều 23</t>
+          <t>h) Ủy ban Tiêu chuẩn Đo lường Chất lượng Quốc gia có trách nhiệm tổ chức triển khai thực hiện các điểm a, b, c, d, đ, e, g khoản này và báo cáo Bộ Khoa học và Công nghệ về kết quả triển khai thực hiện theo quy định về báo cáo định kỳ hoặc yêu cầu báo cáo đột xuất của Bộ Khoa học và Công nghệ.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>152/2020/NĐ-CP</t>
+          <t>Điểm h Khoản 1 Điều 21</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=152669</t>
+          <t>20/2019/TT-BKHCN</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>claude-opus-5-5</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=142713</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>dat</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
+          <t>07/2024/TT-BKHCN</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>actor_has_transitional</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Một người lao động Việt Nam đăng ký dự tuyển làm việc cho tổ chức nước ngoài thì văn bằng, chứng chỉ trong hồ sơ được nộp dưới hình thức bản sao nào?»; nhãn cũ khong_dat group_mismatch: Câu hỏi hỏi hình thức bản sao: cả hai mốc đều là bản sao có chứng thực; chỗ đổi là bản dịch văn bằng nước ngoài được công chứng hoặc chứng thực, câu hỏi không hỏi). Câu hỏi hỏi hình thức xác nhận bản dịch, chạm chỗ đổi</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr"/>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>vilextime:T4:provision:683008bc-eb7e-11f0-8c9f-11c2354deb20:2023-09-18</t>
+          <t>vilextime:T4:provision:3b4128da-2d47-11f1-98ce-1bf21bf5f6be:2021-07-15</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1833,66 +2121,74 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Văn bằng, chứng chỉ do nước ngoài cấp trong hồ sơ dự tuyển của người lao động Việt Nam làm việc cho tổ chức nước ngoài phải được dịch ra tiếng Việt và xác nhận bản dịch theo hình thức nào?</t>
+          <t>Việc đánh giá hồ sơ lựa chọn luật sư ký hợp đồng trợ giúp pháp lý được xác định ra sao về thời hạn hoàn thành và thời gian được kéo dài?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2021-07-15</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Điều 23. Hồ Sơ đăng ký dự tuyển của người lao động Việt Nam</t>
+          <t>2022-03-10 (giua_khoang)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>4. Bản sao có chứng thực văn bằng, chứng chỉ về trình độ chuyên môn kỹ thuật, nghiệp vụ, ngoại ngữ liên quan đến công việc mà người lao động đăng ký dự tuyển. Nếu của nước ngoài thì phải được hợp pháp hóa lãnh sự, trừ trường hợp được miễn hợp pháp hỏa lãnh sự theo điều ước quốc tế mà nước Cộng hòa xã hội chủ nghĩa Việt Nam và nước ngoài liên quan đều là thành viên hoặc theo nguyên tắc có đi có lại hoặc theo quy định của pháp luật; dịch ra tiếng Việt và công chứng hoặc chứng thực theo quy định của pháp luật Việt Nam.</t>
+          <t>Điều 7. Đánh giá hồ sơ và ký hợp đồng với luật sư</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Khoản 4 Điều 23</t>
+          <t>1. Trong thời hạn 10 ngày kể từ ngày hết hạn nộp hồ sơ, Tổ đánh giá luật sư phải hoàn thành việc đánh giá. Trường hợp cần thiết, có thể kéo dài thời gian đánh giá nhưng không quá 03 ngày làm việc.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>152/2020/NĐ-CP</t>
+          <t>Khoản 1 Điều 7</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=152669</t>
+          <t>08/2017/TT-BTP</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>claude-opus-5-5</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=127076</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>dat</t>
+          <t>03/2021/TT-BTP</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Một người lao động Việt Nam đăng ký dự tuyển làm việc cho tổ chức nước ngoài thì văn bằng, chứng chỉ trong hồ sơ được nộp dưới hình thức bản sao nào?»; nhãn cũ khong_dat group_mismatch: Câu hỏi hỏi hình thức bản sao: cả hai mốc đều là bản sao có chứng thực; chỗ đổi là bản dịch văn bằng nước ngoài được công chứng hoặc chứng thực, câu hỏi không hỏi). Câu hỏi hỏi hình thức xác nhận bản dịch, chạm chỗ đổi</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr"/>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>vilextime:T4:provision:68d48650-2d53-11f1-9405-f765f4e15d6f:2025-08-14</t>
+          <t>vilextime:T4:provision:4e5deb4a-2d44-11f1-8275-75d1c87559f7:2025-01-05</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1902,66 +2198,78 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Trường hợp tổ chức, cá nhân không đồng ý với kết quả xác định trước mã số, xuất xứ, trị giá hải quan nhưng cần thông quan hàng hóa, kết quả đó do người đứng đầu cơ quan hải quan cấp nào đưa ra và họ phải làm gì để được thông quan?</t>
+          <t>Nếu một doanh nghiệp đề nghị miễn trừ chất POP, thì bộ nào chủ trì việc đăng ký miễn trừ và có trách nhiệm gì liên quan đến Công ước Stockholm?</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-01-05</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Điều 24. Thủ tục xác định trước mã số, xuất xứ, trị giá hải quan</t>
+          <t>2022-12-28 (giua_khoang)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>4. Văn bản thông báo kết quả xác định trước mã số, xuất xứ, trị giá hải quan là cơ sở để khai hải quan khi làm thủ tục hải quan. Trường hợp tổ chức, cá nhân không đồng ý với nội dung xác định trước mã số, xuất xứ, trị giá hải quan của Tổng cục trưởng Tổng cục Hải quan mà tổ chức, cá nhân cần thiết thông quan hàng hóa thì tổ chức, cá nhân thực hiện nộp thuế theo giá khai báo hoặc thực hiện bảo lãnh theo quy định để thực hiện thông quan hàng hóa. Cơ quan hải quan thực hiện kiểm tra sau thông quan tại cơ quan hải quan.</t>
+          <t>Điều 42. Trách nhiệm của các bộ, cơ quan ngang bộ và Ủy ban nhân dân cấp tỉnh trong quản lý chất ô nhiễm khó phân hủy và nguyên liệu, nhiên liệu, vật liệu, sản phẩm, hàng hóa, thiết bị có chứa chất ô nhiễm khó phân hủy</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Khoản 4 Điều 24</t>
+          <t>1. Bộ Tài nguyên và Môi trường chủ trì, tổ chức thực hiện việc đăng ký miễn trừ các chất POP và kiểm tra, giám sát việc ngừng nhập khẩu, sản xuất, sử dụng các chất POP làm nguyên liệu sản xuất theo quy định về đăng ký miễn trừ các chất POP; đánh giá nhu cầu sản xuất, sử dụng các chất POP; kiểm soát nguồn phát sinh, đánh giá sự phù hợp và kiểm tra đối với chất ô nhiễm khó phân hủy và nguyên liệu, nhiên liệu, vật liệu, sản phẩm, hàng hóa, thiết bị có chứa chất ô nhiễm khó phân hủy theo quy định của pháp luật; ký thỏa thuận công nhận, thừa nhận lẫn nhau về kết quả đánh giá sự phù hợp đối với nguyên liệu, nhiên liệu, vật liệu, sản phẩm, hàng hóa, thiết bị có chứa chất ô nhiễm khó phân hủy với các tổ chức quốc tế, quốc gia có năng lực theo quy định của pháp luật.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>08/2015/NĐ-CP</t>
+          <t>Khoản 1 Điều 42</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=48921</t>
+          <t>08/2022/NĐ-CP</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>claude-opus-5-5</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=168754</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>dat</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
+          <t>05/2025/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>actor_has_transitional</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Khi văn bản thông báo kết quả xác định trước mã số, xuất xứ, trị giá hải quan cần được xem xét lại, cơ quan hải quan cấp nào có thẩm quyền đối với văn bản này?»; nhãn cũ khong_dat question_ambiguous: Việc đề nghị xem xét lại văn bản xác định trước là nội dung khoản 5 cùng Điều; khoản 4 chỉ nói văn bản là cơ sở khai hải quan và cách thông quan khi không đồng ý. Câu hỏi 'cơ quan cấp nào có thẩm quyền đối với văn bản cần xem xét lại' khớp khoản 5 hơn). Câu hỏi không còn hỏi việc xem xét lại (khoản 5); hỏi người ra kết quả và cách thông quan</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr"/>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>vilextime:T4:provision:68d48650-2d53-11f1-9405-f765f4e15d6f:2025-08-15</t>
+          <t>vilextime:T4:provision:4e5deb4a-2d44-11f1-8275-75d1c87559f7:2025-01-06</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1971,66 +2279,78 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Trường hợp tổ chức, cá nhân không đồng ý với kết quả xác định trước mã số, xuất xứ, trị giá hải quan nhưng cần thông quan hàng hóa, kết quả đó do người đứng đầu cơ quan hải quan cấp nào đưa ra và họ phải làm gì để được thông quan?</t>
+          <t>Nếu một doanh nghiệp đề nghị miễn trừ chất POP, thì bộ nào chủ trì việc đăng ký miễn trừ và có trách nhiệm gì liên quan đến Công ước Stockholm?</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-01-06</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Điều 24. Thủ tục xác định trước mã số, xuất xứ, trị giá hải quan</t>
+          <t>2025-09-05 (giua_khoang)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>4. Văn bản thông báo kết quả xác định trước mã số, xuất xứ, trị giá hải quan là cơ sở để khai hải quan khi làm thủ tục hải quan. Trường hợp tổ chức, cá nhân không đồng ý với nội dung xác định trước mã số, xuất xứ, trị giá hải quan của Cục trưởng Cục Hải quan mà tổ chức, cá nhân cần thiết thông quan hàng hóa thì tổ chức, cá nhân thực hiện nộp thuế theo giá khai báo hoặc thực hiện bảo lãnh theo quy định để thực hiện thông quan hàng hóa. Cơ quan hải quan thực hiện kiểm tra sau thông quan tại cơ quan hải quan.</t>
+          <t>Điều 42. Trách nhiệm của các bộ, cơ quan ngang bộ và Ủy ban nhân dân cấp tỉnh trong quản lý chất ô nhiễm khó phân hủy và nguyên liệu, nhiên liệu, vật liệu, sản phẩm, hàng hóa, thiết bị có chứa chất ô nhiễm khó phân hủy</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Khoản 4 Điều 24</t>
+          <t>1. Bộ Tài nguyên và Môi trường chủ trì, tổ chức thực hiện việc đăng ký miễn trừ các chất POP và kiểm tra, giám sát việc ngừng nhập khẩu, sản xuất, sử dụng các chất POP làm nguyên liệu sản xuất theo quy định về đăng ký miễn trừ các chất POP; đánh giá nhu cầu sản xuất, sử dụng các chất POP; kiểm soát nguồn phát sinh, đánh giá sự phù hợp và kiểm tra đối với chất ô nhiễm khó phân hủy và nguyên liệu, nhiên liệu, vật liệu, sản phẩm, hàng hóa, thiết bị có chứa chất ô nhiễm khó phân hủy theo quy định của pháp luật; ký thỏa thuận công nhận, thừa nhận lẫn nhau về kết quả đánh giá sự phù hợp đối với nguyên liệu, nhiên liệu, vật liệu, sản phẩm, hàng hóa, thiết bị có chứa chất ô nhiễm khó phân hủy với các tổ chức quốc tế, quốc gia có năng lực theo quy định của pháp luật; thông báo các thay đổi theo yêu cầu của Công ước Stockholm để thực hiện.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>08/2015/NĐ-CP</t>
+          <t>Khoản 1 Điều 42</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=48921</t>
+          <t>08/2022/NĐ-CP</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>claude-opus-5-5</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=168754</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>dat</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
+          <t>05/2025/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>actor_has_transitional</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Khi văn bản thông báo kết quả xác định trước mã số, xuất xứ, trị giá hải quan cần được xem xét lại, cơ quan hải quan cấp nào có thẩm quyền đối với văn bản này?»; nhãn cũ khong_dat question_ambiguous: Việc đề nghị xem xét lại văn bản xác định trước là nội dung khoản 5 cùng Điều; khoản 4 chỉ nói văn bản là cơ sở khai hải quan và cách thông quan khi không đồng ý. Câu hỏi 'cơ quan cấp nào có thẩm quyền đối với văn bản cần xem xét lại' khớp khoản 5 hơn). Câu hỏi không còn hỏi việc xem xét lại (khoản 5); hỏi người ra kết quả và cách thông quan</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr"/>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>vilextime:T4:provision:6d2c240a-ec3b-11f0-98fa-0d7f046b89cf:2024-11-21</t>
+          <t>vilextime:T4:provision:524dc410-2857-11f1-b228-d7f831690dec:2026-01-08</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2040,66 +2360,74 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sau khi ban hành, quyết định chỉ định tổ chức kiểm định phương tiện đo được gửi tới đâu và được đăng tải trên cổng thông tin điện tử của cơ quan nào?</t>
+          <t>Khi vi phạm quy định về đăng ký, lưu ký, bù trừ chứng khoán bị phạt tiền từ 400.000.000 đồng đến 500.000.000 đồng, những tổ chức nào là đối tượng bị xử phạt?</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Điều 15. Quyết định chỉ định</t>
+          <t>2023-07-28 (giua_khoang)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>3. Quyết định chỉ định được gửi tới tổ chức được chỉ định, Chi cục Tiêu chuẩn Đo lường Chất lượng nơi tổ chức được chỉ định đăng ký trụ sở chính và đăng tải trên cổng thông tin điện tử của Tổng cục.</t>
+          <t>Điều 39. Vi phạm quy định về đăng ký, lưu ký, bù trừ và thanh toán chứng khoán</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Khoản 3 Điều 15</t>
+          <t>5. Phạt tiền từ 400.000.000 đồng đến 500.000.000 đồng đối với Tổng công ty lưu ký và bù trừ chứng khoán Việt Nam, thành viên lưu ký, thành viên bù trừ và phạt tiền từ 200.000.000 đồng đến 250.000.000 đồng đối với nhân viên của thành viên lưu ký, thành viên bù trừ thực hiện hành vi sửa chữa, làm thất lạc chúng từ trong thanh toán, chuyển giao quyền sở hữu chứng khoán.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>24/2013/TT-BKHCN</t>
+          <t>Khoản 5 Điều 39</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=37199</t>
+          <t>156/2020/NĐ-CP</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>claude-opus-5-5</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=146468</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>dat</t>
+          <t>306/2025/NĐ-CP</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Trường hợp một tổ chức được chỉ định kiểm định phương tiện đo, quyết định chỉ định được gửi tới những cơ quan nào?»; nhãn cũ khong_dat group_mismatch: Nơi nhận quyết định (tổ chức được chỉ định, Chi cục Tiêu chuẩn Đo lường Chất lượng) như nhau ở hai mốc; chỗ đổi chỉ là cổng thông tin đăng tải (Tổng cục → Ủy ban), câu hỏi không hỏi tới). Câu hỏi nay hỏi cả cổng đăng tải, chạm chỗ đổi Tổng cục → Ủy ban</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr"/>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>vilextime:T4:provision:6d2c240a-ec3b-11f0-98fa-0d7f046b89cf:2024-11-22</t>
+          <t>vilextime:T4:provision:52a33850-3171-11f1-a40f-5b548501b65a:2025-05-02</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2109,66 +2437,74 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sau khi ban hành, quyết định chỉ định tổ chức kiểm định phương tiện đo được gửi tới đâu và được đăng tải trên cổng thông tin điện tử của cơ quan nào?</t>
+          <t>Khi xây dựng dự thảo chương trình trọng điểm điều tra tài nguyên, môi trường biển, bộ nào tổng hợp, rà soát các dự án, đề án được đề xuất?</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Điều 15. Quyết định chỉ định</t>
+          <t>2026-01-17 (giua_khoang)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>3. Quyết định chỉ định được gửi tới tổ chức được chỉ định, Chi cục Tiêu chuẩn Đo lường Chất lượng nơi tổ chức được chỉ định đăng ký trụ sở chính và đăng tải trên cổng thông tin điện tử của Ủy ban.</t>
+          <t>Điều 24. Tổng hợp, rà soát các dự án, đề án, nhiệm vụ và xây dựng dự thảo chương trình</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Khoản 3 Điều 15</t>
+          <t>1. Bộ Nông nghiệp và Môi trường tổng hợp, rà soát dự án, đề án, nhiệm vụ đưa vào chương trình theo nguyên tắc, căn cứ và yêu cầu quy định tại Điều 20 và Điều 21 Nghị định này.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>24/2013/TT-BKHCN</t>
+          <t>Khoản 1 Điều 24</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=37199</t>
+          <t>40/2016/NĐ-CP</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>claude-opus-5-5</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=110836</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>dat</t>
+          <t>65/2025/NĐ-CP</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Trường hợp một tổ chức được chỉ định kiểm định phương tiện đo, quyết định chỉ định được gửi tới những cơ quan nào?»; nhãn cũ khong_dat group_mismatch: Nơi nhận quyết định (tổ chức được chỉ định, Chi cục Tiêu chuẩn Đo lường Chất lượng) như nhau ở hai mốc; chỗ đổi chỉ là cổng thông tin đăng tải (Tổng cục → Ủy ban), câu hỏi không hỏi tới). Câu hỏi nay hỏi cả cổng đăng tải, chạm chỗ đổi Tổng cục → Ủy ban</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr"/>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>vilextime:T4:provision:6f540750-df45-11f0-bdb0-173fc9978251#k2#a:2015-09-30</t>
+          <t>vilextime:T4:provision:55ac5bec-df4d-11f0-b470-a3516d537d9d#k1#b:2023-02-28</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2178,66 +2514,74 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Khi Chấp hành viên của cơ quan thi hành án dân sự không thuộc quân đội gửi báo cáo thống kê kết quả thi hành án của kỳ trước cho Thủ trưởng cơ quan nơi công tác, thời hạn chậm nhất là trước ngày nào của kỳ báo cáo kế tiếp?</t>
+          <t>Theo quy định về thay đổi tên của tổ chức tín dụng là hợp tác xã, hồ sơ phải có văn bản nào của Đại hội thành viên?</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2015-09-30</t>
+          <t>2023-02-28</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2. Thời hạn gửi báo cáo thống kê thi hành án dân sự:</t>
+          <t>2019-11-10 (giua_khoang); 2026-03-13 (sau_het_hieu_luc)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>a) Chậm nhất trước ngày 03 của kỳ báo cáo kế tiếp, Chấp hành viên gửi báo cáo thống kê kết quả thi hành án của kỳ trước cho Thủ trưởng cơ quan Thi hành án dân sự nơi công tác;</t>
+          <t>1. Hồ sơ đề nghị gồm:</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Điểm a Khoản 2 Điều 10</t>
+          <t>b) Quyết định của Đại hội thành viên thông qua việc thay đổi tên.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>01/2013/TT-BTP</t>
+          <t>Điểm b Khoản 1 Điều 5</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=30308</t>
+          <t>05/2018/TT-NHNN</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>claude-opus-5-5</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=128193</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>dat</t>
+          <t>22/2022/TT-NHNN</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Khi Chấp hành viên gửi báo cáo thống kê kết quả thi hành án của kỳ trước, thời hạn chậm nhất là trước ngày nào của kỳ báo cáo kế tiếp?»; nhãn cũ khong_dat question_ambiguous: Câu hỏi không phân biệt Chấp hành viên dân sự (điểm a) với Chấp hành viên thi hành án dân sự trong quân đội (điểm d, vẫn trước ngày 03); ở mốc 2 hai điểm cho hai đáp án khác nhau). Câu hỏi loại Chấp hành viên trong quân đội (điểm d)</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr"/>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>vilextime:T4:provision:6f540750-df45-11f0-bdb0-173fc9978251#k2#a:2015-10-01</t>
+          <t>vilextime:T4:provision:5cc79b52-ec41-11f0-95e4-0f1dfe7bb184#k2#b:2015-06-30</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2247,66 +2591,78 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Khi Chấp hành viên của cơ quan thi hành án dân sự không thuộc quân đội gửi báo cáo thống kê kết quả thi hành án của kỳ trước cho Thủ trưởng cơ quan nơi công tác, thời hạn chậm nhất là trước ngày nào của kỳ báo cáo kế tiếp?</t>
+          <t>Những người nào được cấp Giấy chứng nhận vùng hoạt động hoa tiêu hàng hải tại một vùng hoạt động và tuyến dẫn tàu căn cứ vào kinh nghiệm đã có tại vùng, tuyến đó?</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2015-10-01</t>
+          <t>2015-06-30</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2. Thời hạn gửi báo cáo thống kê thi hành án dân sự:</t>
+          <t>2014-06-05 (giua_khoang); 2018-09-14 (sau_het_hieu_luc)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>a) Chậm nhất trước ngày 02 của kỳ báo cáo kế tiếp, Chấp hành viên gửi báo cáo thống kê kết quả thi hành án của kỳ trước cho Thủ trưởng cơ quan Thi hành án dân sự nơi công tác;</t>
+          <t>2. Giấy chứng nhận vùng hoạt động hoa tiêu hàng hải</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Điểm a Khoản 2 Điều 10</t>
+          <t>b) Hoa tiêu hàng hải đã qua thực tập dẫn tàu ở vùng hoạt động và tuyến dẫn tàu nào thì được cấp GCNVHĐHTHH tại vùng hoạt động và tuyến dẫn tàu đó.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>01/2013/TT-BTP</t>
+          <t>Điểm b Khoản 2 Điều 2</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=30308</t>
+          <t>36/2013/TT-BGTVT</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>claude-opus-5-5</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=37793</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>dat</t>
+          <t>16/2015/TT-BGTVT</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Khi Chấp hành viên gửi báo cáo thống kê kết quả thi hành án của kỳ trước, thời hạn chậm nhất là trước ngày nào của kỳ báo cáo kế tiếp?»; nhãn cũ khong_dat question_ambiguous: Câu hỏi không phân biệt Chấp hành viên dân sự (điểm a) với Chấp hành viên thi hành án dân sự trong quân đội (điểm d, vẫn trước ngày 03); ở mốc 2 hai điểm cho hai đáp án khác nhau). Câu hỏi loại Chấp hành viên trong quân đội (điểm d)</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr"/>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Trường hợp cấp Giấy chứng nhận vùng hoạt động hoa tiêu hàng hải cho một vùng và tuyến dẫn tàu cụ thể, người được cấp phải đáp ứng điều kiện gì về thực tập dẫn tàu?»; nhãn cũ khong_dat group_mismatch: Với hoa tiêu, điều kiện thực tập dẫn tàu như nhau ở hai mốc; chỗ đổi thêm trường hợp thuyền trưởng đã dẫn tàu, câu hỏi không hỏi). Câu hỏi hỏi những người được cấp theo kinh nghiệm, chạm chỗ thêm thuyền trưởng</t>
+        </is>
+      </c>
       <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>vilextime:T4:provision:6f603d84-e177-11f0-9fb9-2be267cb8d07:2024-12-19</t>
+          <t>vilextime:T4:provision:5cc79b52-ec41-11f0-95e4-0f1dfe7bb184#k2#b:2015-07-01</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2316,66 +2672,78 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Theo quy định về đầu tư nâng cao năng lực, lực lượng cảnh sát nào được đầu tư cơ sở vật chất, phương tiện, thiết bị kỹ thuật để đấu tranh với tội phạm, vi phạm trong lĩnh vực môi trường?</t>
+          <t>Những người nào được cấp Giấy chứng nhận vùng hoạt động hoa tiêu hàng hải tại một vùng hoạt động và tuyến dẫn tàu căn cứ vào kinh nghiệm đã có tại vùng, tuyến đó?</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2015-07-01</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Điều 16. Đầu tư nâng cao năng lực cho Cảnh sát môi trường</t>
+          <t>2016-01-30 (giua_khoang)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2. Cảnh sát môi trường được đầu tư cơ sở vật chất, trụ sở làm việc, phương tiện, thiết bị kỹ thuật đáp ứng yêu cầu công tác phòng, chống tội phạm và vi phạm hành chính về môi trường, tài nguyên, an toàn thực phẩm.</t>
+          <t>2. Giấy chứng nhận vùng hoạt động hoa tiêu hàng hải</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Khoản 2 Điều 16</t>
+          <t>b) Hoa tiêu hàng hải đã qua thực tập dẫn tàu, thuyền trưởng đã dẫn tàu ở vùng hoạt động và tuyến dẫn tàu nào thì được cấp GCNVHĐHTHH tại vùng hoạt động và tuyến dẫn tàu đó.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>105/2015/NĐ-CP</t>
+          <t>Điểm b Khoản 2 Điều 2</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=92155</t>
+          <t>36/2013/TT-BGTVT</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>claude-opus-5-5</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=37793</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>dat</t>
+          <t>16/2015/TT-BGTVT</t>
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Trường hợp đầu tư nâng cao năng lực cho Cảnh sát môi trường, lực lượng này được đầu tư những gì và để đáp ứng yêu cầu công tác nào?»; nhãn cũ khong_dat group_mismatch: Nội dung đầu tư và yêu cầu công tác như nhau ở hai mốc; chỉ đổi tên lực lượng). Câu hỏi hỏi tên lực lượng, không chép tên</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr"/>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Trường hợp cấp Giấy chứng nhận vùng hoạt động hoa tiêu hàng hải cho một vùng và tuyến dẫn tàu cụ thể, người được cấp phải đáp ứng điều kiện gì về thực tập dẫn tàu?»; nhãn cũ khong_dat group_mismatch: Với hoa tiêu, điều kiện thực tập dẫn tàu như nhau ở hai mốc; chỗ đổi thêm trường hợp thuyền trưởng đã dẫn tàu, câu hỏi không hỏi). Câu hỏi hỏi những người được cấp theo kinh nghiệm, chạm chỗ thêm thuyền trưởng</t>
+        </is>
+      </c>
       <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>vilextime:T4:provision:6f603d84-e177-11f0-9fb9-2be267cb8d07:2024-12-20</t>
+          <t>vilextime:T4:provision:5cc8108c-ec41-11f0-8296-c3595dfdbe4b#k1#a:2015-06-30</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2385,66 +2753,78 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Theo quy định về đầu tư nâng cao năng lực, lực lượng cảnh sát nào được đầu tư cơ sở vật chất, phương tiện, thiết bị kỹ thuật để đấu tranh với tội phạm, vi phạm trong lĩnh vực môi trường?</t>
+          <t>Trong lĩnh vực hoa tiêu hàng hải, đơn đề nghị cấp lại giấy chứng nhận khả năng chuyên môn phải có xác nhận của người đứng đầu những đơn vị nào?</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2024-12-20</t>
+          <t>2015-06-30</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Điều 16. Đầu tư nâng cao năng lực cho Cảnh sát môi trường</t>
+          <t>2015-04-13 (giua_khoang); 2025-03-17 (sau_het_hieu_luc)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2. lực lượng Cảnh sát phòng, chống tội phạm về môi trường được đầu tư cơ sở vật chất, trụ sở làm việc, phương tiện, thiết bị kỹ thuật đáp ứng yêu cầu công tác phòng, chống tội phạm và vi phạm hành chính về môi trường, tài nguyên, an toàn thực phẩm.</t>
+          <t>1. Thành phần hồ sơ cấp lại GCNKNCMHTHH:</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Khoản 2 Điều 16</t>
+          <t>a) Đơn đề nghị cấp lại GCNKNCMHTHH, trong đó nêu rõ lý do và có xác nhận của người đứng đầu tổ chức hoa tiêu hàng hải theo mẫu quy định tại Phụ lục 6 của Thông tư này;</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>105/2015/NĐ-CP</t>
+          <t>Điểm a Khoản 1 Điều 15</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=92155</t>
+          <t>36/2013/TT-BGTVT</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>claude-opus-5-5</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=37793</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>dat</t>
+          <t>16/2015/TT-BGTVT</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Trường hợp đầu tư nâng cao năng lực cho Cảnh sát môi trường, lực lượng này được đầu tư những gì và để đáp ứng yêu cầu công tác nào?»; nhãn cũ khong_dat group_mismatch: Nội dung đầu tư và yêu cầu công tác như nhau ở hai mốc; chỉ đổi tên lực lượng). Câu hỏi hỏi tên lực lượng, không chép tên</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr"/>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>lineage thay thế 29/09; câu hỏi và đáp án ngắn do cùng model viết</t>
+        </is>
+      </c>
       <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>vilextime:T4:provision:9d44166a-2e81-11f1-8975-ef6a7728f53c:2025-07-20</t>
+          <t>vilextime:T4:provision:5cc8108c-ec41-11f0-8296-c3595dfdbe4b#k1#a:2015-07-01</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2454,62 +2834,78 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Trường hợp cần hướng dẫn thực hiện chế độ cho đối tượng mới được bổ sung, những bộ nào phải ban hành thông tư liên tịch?</t>
+          <t>Trong lĩnh vực hoa tiêu hàng hải, đơn đề nghị cấp lại giấy chứng nhận khả năng chuyên môn phải có xác nhận của người đứng đầu những đơn vị nào?</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2015-07-01</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Điều 3. Trách nhiệm thi hành</t>
+          <t>2016-02-17 (giua_khoang)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2. Bộ Công an, Bộ Lao động - Thương binh và Xã hội, Bộ Tài chính ban hành Thông tư liên tịch hướng dẫn thực hiện chế độ đối với đối tượng quy định tại khoản 3 Điều 1 Nghị định này.</t>
+          <t>1. Thành phần hồ sơ cấp lại GCNKNCMHTHH:</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Khoản 2 Điều 3</t>
+          <t>a) Đơn đề nghị cấp lại GCNKNCMHTHH, trong đó nêu rõ lý do và có xác nhận của người đứng đầu tổ chức hoa tiêu hàng hải hoặc đơn vị quản lý thuyền trưởng theo mẫu quy định tại Phụ lục 6 của Thông tư này;</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>11/2011/NĐ-CP</t>
+          <t>Điểm a Khoản 1 Điều 15</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=26088</t>
+          <t>36/2013/TT-BGTVT</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>claude-opus-5-5</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=37793</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>dat</t>
+          <t>16/2015/TT-BGTVT</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>lineage thay thế 29/09; câu hỏi và đáp án ngắn do cùng model viết</t>
+        </is>
+      </c>
       <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>vilextime:T4:provision:a324f2cc-df4c-11f0-894a-8ddf853d159d:2024-01-31</t>
+          <t>vilextime:T4:provision:60e5a770-2c82-11f1-91d8-05743c0a6064:2024-11-21</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2519,62 +2915,78 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Trong lĩnh vực quản lý rừng bền vững, Sở Nông nghiệp và Phát triển nông thôn phải báo cáo kết quả hằng năm trước ngày nào và gửi cho đơn vị nào thuộc Bộ?</t>
+          <t>Trường hợp hồ sơ đăng ký cơ sở pha chế xăng dầu đầy đủ, hợp lệ, cơ quan nào cấp Giấy chứng nhận đăng ký cho thương nhân đầu mối?</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2024-01-31</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>3. Sở Nông nghiệp và Phát triển nông thôn:</t>
+          <t>2019-06-11 (giua_khoang)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>c) Hằng năm trước ngày 15 tháng 12, báo cáo Ủy ban nhân dân cấp tỉnh và Bộ Nông nghiệp và Phát triển nông thôn (Tổng cục Lâm nghiệp) kết quả xây dựng và thực hiện phương án quản lý rừng bền vững và cấp chứng chỉ quản lý rừng bền vững trên địa bàn tỉnh.</t>
+          <t>2. Thẩm xét hồ sơ và cấp Giấy chứng nhận đăng ký cơ sở pha chế xăng dầu:</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Điểm c Khoản 3 Điều 18</t>
+          <t>b) Trường hợp hồ sơ đầy đủ, hợp lệ, trong thời hạn bảy (07) ngày làm việc kể từ ngày tiếp nhận hồ sơ của thương nhân đầu mối, Tổng cục Tiêu chuẩn Đo lường Chất lượng cấp Giấy chứng nhận đăng ký cơ sở pha chế xăng dầu (theo Mẫu 4. GCN quy định tại Phụ lục kèm theo Thông tư này) cho cơ sở pha chế xăng dầu với thời hạn hiệu lực không quá năm (05) năm kể từ ngày cấp. Trường hợp hồ sơ chưa đáp ứng yêu cầu, cần phải thẩm định thực tế, trong thời hạn ba mươi (30) ngày làm việc kể từ khi nhận được hồ sơ đầy đủ, Tổng cục Tiêu chuẩn Đo lường Chất lượng tiến hành thẩm xét hồ sơ, cử chuyên gia hoặc thành lập đoàn thẩm định thực tế tại thương nhân đầu mối. Chi phí phục vụ hoạt động thẩm định của chuyên gia hoặc đoàn thẩm định do thương nhân đầu mối chi trả theo quy định của pháp luật hiện hành. Căn cứ hồ sơ đăng ký, biên bản thẩm định thực tế và kết quả thực hiện hành động khắc phục đạt yêu cầu (nếu có), trong thời hạn mười (10) ngày làm việc, Tổng cục Tiêu chuẩn Đo lường Chất lượng cấp Giấy chứng nhận đăng ký cơ sở pha chế xăng dầu (theo Mẫu 4. GCN quy định tại Phụ lục kèm theo Thông tư này) cho cơ sở pha chế xăng dầu với thời hạn hiệu lực không quá năm (05) năm kể từ ngày cấp. Trong trường hợp từ chối cấp giấy chứng nhận, trong thời hạn mười (10) ngày làm việc, Tổng cục Tiêu chuẩn Đo lường Chất lượng; thông báo lý do từ chối bằng văn bản cho thương nhân đầu mối;</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>28/2018/TT-BNNPTNT</t>
+          <t>Điểm b Khoản 2 Điều 16</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=133923</t>
+          <t>15/2015/TT-BKHCN</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>claude-opus-5-5</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=86534</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>dat</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
+          <t>07/2024/TT-BKHCN</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>actor_has_transitional</t>
+        </is>
+      </c>
       <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>vilextime:T4:provision:ada68200-2d45-11f1-95b6-e35525714d94:2024-11-21</t>
+          <t>vilextime:T4:provision:60e5a770-2c82-11f1-91d8-05743c0a6064:2024-11-22</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2584,66 +2996,78 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sau khi kế hoạch 5 năm xây dựng TCVN được phê duyệt, kế hoạch phải được công khai trên cổng thông tin điện tử của những cơ quan nào và trong thời hạn bao lâu?</t>
+          <t>Trường hợp hồ sơ đăng ký cơ sở pha chế xăng dầu đầy đủ, hợp lệ, cơ quan nào cấp Giấy chứng nhận đăng ký cho thương nhân đầu mối?</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2. Kế hoạch 5 năm xây dựng TCVN Nội dung kế hoạch 5 năm xây dựng TCVN bao gồm: lĩnh vực, đối tượng cụ thể cần xây dựng TCVN; loại tiêu chuẩn; số lượng TCVN cần xây dựng; thời gian thực hiện; nguồn kinh phí và kinh phí dự kiến. Lập, phê duyệt, điều chỉnh, bổ sung kế hoạch 5 năm xây dựng TCVN thực hiện theo trình tự sau đây:</t>
+          <t>2025-11-24 (giua_khoang)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>c) Phê duyệt kế hoạch 5 năm Bộ trưởng Bộ Khoa học và Công nghệ tổ chức xem xét, phê duyệt kế hoạch 5 năm xây dựng TCVN. Bộ Khoa học và Công nghệ thông báo kế hoạch đã được phê duyệt đến các bộ, ngành, tổ chức liên quan và công khai trên Cổng thông tin điện tử của Bộ Khoa học và Công nghệ, Cổng thông tin điện tử của Tổng cục Tiêu chuẩn Đo lường Chất lượng trong thời hạn 30 (ba mươi) ngày, kể từ ngày kế hoạch được phê duyệt;</t>
+          <t>2. Thẩm xét hồ sơ và cấp Giấy chứng nhận đăng ký cơ sở pha chế xăng dầu:</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Điểm c Khoản 2 Điều 4</t>
+          <t>b) Trường hợp hồ sơ đầy đủ, hợp lệ, trong thời hạn bảy (07) ngày làm việc kể từ ngày tiếp nhận hồ sơ của thương nhân đầu mối, Ủy ban Tiêu chuẩn Đo lường Chất lượng Quốc gia cấp Giấy chứng nhận đăng ký cơ sở pha chế xăng dầu (theo Mẫu 4. GCN quy định tại Phụ lục kèm theo Thông tư này) cho cơ sở pha chế xăng dầu với thời hạn hiệu lực không quá năm (05) năm kể từ ngày cấp. Trường hợp hồ sơ chưa đáp ứng yêu cầu, cần phải thẩm định thực tế, trong thời hạn ba mươi (30) ngày làm việc kể từ khi nhận được hồ sơ đầy đủ, Ủy ban Tiêu chuẩn Đo lường Chất lượng Quốc gia tiến hành thẩm xét hồ sơ, cử chuyên gia hoặc thành lập đoàn thẩm định thực tế tại thương nhân đầu mối. Chi phí phục vụ hoạt động thẩm định của chuyên gia hoặc đoàn thẩm định do thương nhân đầu mối chi trả theo quy định của pháp luật hiện hành. Căn cứ hồ sơ đăng ký, biên bản thẩm định thực tế và kết quả thực hiện hành động khắc phục đạt yêu cầu (nếu có), trong thời hạn mười (10) ngày làm việc, Ủy ban Tiêu chuẩn Đo lường Chất lượng Quốc gia cấp Giấy chứng nhận đăng ký cơ sở pha chế xăng dầu (theo Mẫu 4. GCN quy định tại Phụ lục kèm theo Thông tư này) cho cơ sở pha chế xăng dầu với thời hạn hiệu lực không quá năm (05) năm kể từ ngày cấp. Trong trường hợp từ chối cấp giấy chứng nhận, trong thời hạn mười (10) ngày làm việc, Ủy ban Tiêu chuẩn Đo lường Chất lượng Quốc gia; thông báo lý do từ chối bằng văn bản cho thương nhân đầu mối;</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>11/2021/TT-BKHCN</t>
+          <t>Điểm b Khoản 2 Điều 16</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=152575</t>
+          <t>15/2015/TT-BKHCN</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>claude-opus-5-5</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=86534</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>dat</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr"/>
+          <t>07/2024/TT-BKHCN</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>actor_has_transitional</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Pháp luật về xây dựng và áp dụng tiêu chuẩn quy định cơ quan nào phối hợp trong việc xây dựng và thông báo kế hoạch 5 năm xây dựng TCVN?»; nhãn cũ khong_dat question_ambiguous: 'Cơ quan nào phối hợp trong việc xây dựng và thông báo kế hoạch' không ghim được chỗ đổi (cổng thông tin công khai); điểm b cùng khoản giao Tổng cục lấy ý kiến, hoàn chỉnh dự thảo kế hoạch, và điểm c do Bộ trưởng phê duyệt, Bộ thông báo). Câu hỏi chốt việc công khai sau phê duyệt (điểm c), chạm chỗ đổi</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr"/>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>vilextime:T4:provision:ada68200-2d45-11f1-95b6-e35525714d94:2024-11-22</t>
+          <t>vilextime:T4:provision:683008bc-eb7e-11f0-8c9f-11c2354deb20:2023-09-17</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2653,66 +3077,78 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sau khi kế hoạch 5 năm xây dựng TCVN được phê duyệt, kế hoạch phải được công khai trên cổng thông tin điện tử của những cơ quan nào và trong thời hạn bao lâu?</t>
+          <t>Văn bằng, chứng chỉ do nước ngoài cấp trong hồ sơ dự tuyển của người lao động Việt Nam làm việc cho tổ chức nước ngoài phải được dịch ra tiếng Việt và xác nhận bản dịch theo hình thức nào?</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2. Kế hoạch 5 năm xây dựng TCVN Nội dung kế hoạch 5 năm xây dựng TCVN bao gồm: lĩnh vực, đối tượng cụ thể cần xây dựng TCVN; loại tiêu chuẩn; số lượng TCVN cần xây dựng; thời gian thực hiện; nguồn kinh phí và kinh phí dự kiến. Lập, phê duyệt, điều chỉnh, bổ sung kế hoạch 5 năm xây dựng TCVN thực hiện theo trình tự sau đây:</t>
+          <t>2021-08-14 (giua_khoang)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>c) Phê duyệt kế hoạch 5 năm Bộ trưởng Bộ Khoa học và Công nghệ tổ chức xem xét, phê duyệt kế hoạch 5 năm xây dựng TCVN. Bộ Khoa học và Công nghệ thông báo kế hoạch đã được phê duyệt đến các bộ, ngành, tổ chức liên quan và công khai trên Cổng thông tin điện tử của Bộ Khoa học và Công nghệ, Cổng thông tin điện tử của Ủy ban Tiêu chuẩn Đo lường Chất lượng Quốc gia trong thời hạn 30 (ba mươi) ngày, kể từ ngày kế hoạch được phê duyệt;</t>
+          <t>Điều 23. Hồ Sơ đăng ký dự tuyển của người lao động Việt Nam</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Điểm c Khoản 2 Điều 4</t>
+          <t>4. Bản sao có chứng thực văn bằng, chứng chỉ về trình độ chuyên môn kỹ thuật, nghiệp vụ, ngoại ngữ liên quan đến công việc mà người lao động đăng ký dự tuyển. Nếu của nước ngoài thì phải được hợp pháp hóa lãnh sự, trừ trường hợp được miễn hợp pháp hỏa lãnh sự theo điều ước quốc tế mà nước Cộng hòa xã hội chủ nghĩa Việt Nam và nước ngoài liên quan đều là thành viên hoặc theo nguyên tắc có đi có lại hoặc theo quy định của pháp luật; dịch ra tiếng Việt và chứng thực theo quy định của pháp luật Việt Nam.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>11/2021/TT-BKHCN</t>
+          <t>Khoản 4 Điều 23</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=152575</t>
+          <t>152/2020/NĐ-CP</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>claude-opus-5-5</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=152669</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>dat</t>
+          <t>70/2023/NĐ-CP</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Pháp luật về xây dựng và áp dụng tiêu chuẩn quy định cơ quan nào phối hợp trong việc xây dựng và thông báo kế hoạch 5 năm xây dựng TCVN?»; nhãn cũ khong_dat question_ambiguous: 'Cơ quan nào phối hợp trong việc xây dựng và thông báo kế hoạch' không ghim được chỗ đổi (cổng thông tin công khai); điểm b cùng khoản giao Tổng cục lấy ý kiến, hoàn chỉnh dự thảo kế hoạch, và điểm c do Bộ trưởng phê duyệt, Bộ thông báo). Câu hỏi chốt việc công khai sau phê duyệt (điểm c), chạm chỗ đổi</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr"/>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Một người lao động Việt Nam đăng ký dự tuyển làm việc cho tổ chức nước ngoài thì văn bằng, chứng chỉ trong hồ sơ được nộp dưới hình thức bản sao nào?»; nhãn cũ khong_dat group_mismatch: Câu hỏi hỏi hình thức bản sao: cả hai mốc đều là bản sao có chứng thực; chỗ đổi là bản dịch văn bằng nước ngoài được công chứng hoặc chứng thực, câu hỏi không hỏi). Câu hỏi hỏi hình thức xác nhận bản dịch, chạm chỗ đổi</t>
+        </is>
+      </c>
       <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>vilextime:T4:provision:bcce4ee0-2f37-11f1-927e-c7ac35ffa800:2024-11-14</t>
+          <t>vilextime:T4:provision:683008bc-eb7e-11f0-8c9f-11c2354deb20:2023-09-18</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2722,62 +3158,78 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Thẩm quyền áp dụng biện pháp khắc phục hậu quả của Chủ tịch Ủy ban nhân dân cấp huyện trong lĩnh vực bổ trợ tư pháp được xác định ra sao?</t>
+          <t>Văn bằng, chứng chỉ do nước ngoài cấp trong hồ sơ dự tuyển của người lao động Việt Nam làm việc cho tổ chức nước ngoài phải được dịch ra tiếng Việt và xác nhận bản dịch theo hình thức nào?</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2. Chủ tịch Ủy ban nhân dân cấp huyện có quyền:</t>
+          <t>2025-05-11 (giua_khoang)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>d) Áp dụng biện pháp khắc phục hậu quả quy định tại các điểm a, e và i khoản 1 Điều 28 Luật Xử lý vi phạm hành chính; các điểm a, b, đ, l, m và n khoản 3 Điều 3 Nghị định này.</t>
+          <t>Điều 23. Hồ Sơ đăng ký dự tuyển của người lao động Việt Nam</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Điểm d Khoản 2 Điều 83</t>
+          <t>4. Bản sao có chứng thực văn bằng, chứng chỉ về trình độ chuyên môn kỹ thuật, nghiệp vụ, ngoại ngữ liên quan đến công việc mà người lao động đăng ký dự tuyển. Nếu của nước ngoài thì phải được hợp pháp hóa lãnh sự, trừ trường hợp được miễn hợp pháp hỏa lãnh sự theo điều ước quốc tế mà nước Cộng hòa xã hội chủ nghĩa Việt Nam và nước ngoài liên quan đều là thành viên hoặc theo nguyên tắc có đi có lại hoặc theo quy định của pháp luật; dịch ra tiếng Việt và công chứng hoặc chứng thực theo quy định của pháp luật Việt Nam.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>82/2020/NĐ-CP</t>
+          <t>Khoản 4 Điều 23</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=143024</t>
+          <t>152/2020/NĐ-CP</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>claude-opus-5-5</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=152669</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>dat</t>
+          <t>70/2023/NĐ-CP</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Một người lao động Việt Nam đăng ký dự tuyển làm việc cho tổ chức nước ngoài thì văn bằng, chứng chỉ trong hồ sơ được nộp dưới hình thức bản sao nào?»; nhãn cũ khong_dat group_mismatch: Câu hỏi hỏi hình thức bản sao: cả hai mốc đều là bản sao có chứng thực; chỗ đổi là bản dịch văn bằng nước ngoài được công chứng hoặc chứng thực, câu hỏi không hỏi). Câu hỏi hỏi hình thức xác nhận bản dịch, chạm chỗ đổi</t>
+        </is>
+      </c>
       <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>vilextime:T4:provision:bdb196ac-df3f-11f0-a53b-49fbe419b389:2025-06-23</t>
+          <t>vilextime:T4:provision:68d48650-2d53-11f1-9405-f765f4e15d6f:2025-08-14</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2787,62 +3239,78 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Khi hoạt động của bãi cất, hạ cánh trên boong tàu vi phạm điều kiện, quyết định đóng bãi phải được thông báo cho những bộ nào?</t>
+          <t>Trường hợp tổ chức, cá nhân không đồng ý với kết quả xác định trước mã số, xuất xứ, trị giá hải quan nhưng cần thông quan hàng hóa, kết quả đó do người đứng đầu cơ quan hải quan cấp nào đưa ra và họ phải làm gì để được thông quan?</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Điều 16. Trình tự, thủ tục đóng bãi cất, hạ cánh trên boong tàu</t>
+          <t>2015-10-15 (giua_khoang)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>3. Khi hoạt động của bãi cất, hạ cánh vi phạm một trong các điều kiện quy định tại điểm a, b, c, d, đ của khoản 2 Điều 10; Bộ Tổng Tham mưu ra quyết định đóng bãi cất, hạ cánh và thông báo với Bộ Xây dựng, chủ sở hữu tàu và các cơ quan, tổ chức, cá nhân liên quan.</t>
+          <t>Điều 24. Thủ tục xác định trước mã số, xuất xứ, trị giá hải quan</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Khoản 3 Điều 16</t>
+          <t>4. Văn bản thông báo kết quả xác định trước mã số, xuất xứ, trị giá hải quan là cơ sở để khai hải quan khi làm thủ tục hải quan. Trường hợp tổ chức, cá nhân không đồng ý với nội dung xác định trước mã số, xuất xứ, trị giá hải quan của Tổng cục trưởng Tổng cục Hải quan mà tổ chức, cá nhân cần thiết thông quan hàng hóa thì tổ chức, cá nhân thực hiện nộp thuế theo giá khai báo hoặc thực hiện bảo lãnh theo quy định để thực hiện thông quan hàng hóa. Cơ quan hải quan thực hiện kiểm tra sau thông quan tại cơ quan hải quan.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>42/2016/NĐ-CP</t>
+          <t>Khoản 4 Điều 24</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=141668</t>
+          <t>08/2015/NĐ-CP</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>claude-opus-5-5</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=48921</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>dat</t>
+          <t>167/2025/NĐ-CP</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Khi văn bản thông báo kết quả xác định trước mã số, xuất xứ, trị giá hải quan cần được xem xét lại, cơ quan hải quan cấp nào có thẩm quyền đối với văn bản này?»; nhãn cũ khong_dat question_ambiguous: Việc đề nghị xem xét lại văn bản xác định trước là nội dung khoản 5 cùng Điều; khoản 4 chỉ nói văn bản là cơ sở khai hải quan và cách thông quan khi không đồng ý. Câu hỏi 'cơ quan cấp nào có thẩm quyền đối với văn bản cần xem xét lại' khớp khoản 5 hơn). Câu hỏi không còn hỏi việc xem xét lại (khoản 5); hỏi người ra kết quả và cách thông quan</t>
+        </is>
+      </c>
       <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>vilextime:T4:provision:dcf457d0-3b96-11f1-b174-b5c1cf7b0c30:2026-08-09</t>
+          <t>vilextime:T4:provision:68d48650-2d53-11f1-9405-f765f4e15d6f:2025-08-15</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2852,66 +3320,78 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Trước khi mở tuyến xe buýt đi đến hoặc xuất phát từ khu vực cảng hàng không, Ủy ban nhân dân cấp tỉnh phải thống nhất với bộ nào?</t>
+          <t>Trường hợp tổ chức, cá nhân không đồng ý với kết quả xác định trước mã số, xuất xứ, trị giá hải quan nhưng cần thông quan hàng hóa, kết quả đó do người đứng đầu cơ quan hải quan cấp nào đưa ra và họ phải làm gì để được thông quan?</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Điều 73. Ủy ban nhân dân cấp tỉnh</t>
+          <t>2026-05-29 (giua_khoang)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2. Phối hợp với Ủy ban nhân dân cấp tỉnh có tuyến xe buýt đi qua để thống nhất thực hiện các nhiệm vụ nêu tại khoản 3 Điều 5 của Nghị định này. Thống nhất với Bộ Giao thông vận tải trước khi mở tuyến xe buýt có điểm đầu hoặc điểm cuối nằm trong khu vực cảng hàng không.</t>
+          <t>Điều 24. Thủ tục xác định trước mã số, xuất xứ, trị giá hải quan</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Khoản 2 Điều 73</t>
+          <t>4. Văn bản thông báo kết quả xác định trước mã số, xuất xứ, trị giá hải quan là cơ sở để khai hải quan khi làm thủ tục hải quan. Trường hợp tổ chức, cá nhân không đồng ý với nội dung xác định trước mã số, xuất xứ, trị giá hải quan của Cục trưởng Cục Hải quan mà tổ chức, cá nhân cần thiết thông quan hàng hóa thì tổ chức, cá nhân thực hiện nộp thuế theo giá khai báo hoặc thực hiện bảo lãnh theo quy định để thực hiện thông quan hàng hóa. Cơ quan hải quan thực hiện kiểm tra sau thông quan tại cơ quan hải quan.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>158/2024/NĐ-CP</t>
+          <t>Khoản 4 Điều 24</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=173412</t>
+          <t>08/2015/NĐ-CP</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>claude-opus-5-5</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=48921</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>dat</t>
+          <t>167/2025/NĐ-CP</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Khi Ủy ban nhân dân cấp tỉnh thực hiện nhiệm vụ quản lý vận tải đường bộ, cơ quan chuyên môn về giao thông ở địa phương được gọi tên theo sở nào?»; nhãn cũ khong_dat unanswerable_as_asked: Câu hỏi hỏi 'cơ quan chuyên môn về giao thông ở địa phương được gọi tên theo sở nào', nhưng khoản 2 không nói về sở; chỗ đổi là Bộ phải thống nhất trước khi mở tuyến xe buýt vào cảng hàng không (Bộ Giao thông vận tải → Bộ Xây dựng)). Câu hỏi hỏi bộ phải thống nhất, chạm chỗ đổi</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr"/>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Khi văn bản thông báo kết quả xác định trước mã số, xuất xứ, trị giá hải quan cần được xem xét lại, cơ quan hải quan cấp nào có thẩm quyền đối với văn bản này?»; nhãn cũ khong_dat question_ambiguous: Việc đề nghị xem xét lại văn bản xác định trước là nội dung khoản 5 cùng Điều; khoản 4 chỉ nói văn bản là cơ sở khai hải quan và cách thông quan khi không đồng ý. Câu hỏi 'cơ quan cấp nào có thẩm quyền đối với văn bản cần xem xét lại' khớp khoản 5 hơn). Câu hỏi không còn hỏi việc xem xét lại (khoản 5); hỏi người ra kết quả và cách thông quan</t>
+        </is>
+      </c>
       <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>vilextime:T4:provision:dcf457d0-3b96-11f1-b174-b5c1cf7b0c30:2026-08-10</t>
+          <t>vilextime:T4:provision:6d2c240a-ec3b-11f0-98fa-0d7f046b89cf:2024-11-21</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2921,66 +3401,82 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Trước khi mở tuyến xe buýt đi đến hoặc xuất phát từ khu vực cảng hàng không, Ủy ban nhân dân cấp tỉnh phải thống nhất với bộ nào?</t>
+          <t>Sau khi ban hành, quyết định chỉ định tổ chức kiểm định phương tiện đo được gửi tới đâu và được đăng tải trên cổng thông tin điện tử của cơ quan nào?</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Điều 73. Ủy ban nhân dân cấp tỉnh</t>
+          <t>2022-01-26 (giua_khoang); 2026-07-04 (sau_het_hieu_luc)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2. Phối hợp với Ủy ban nhân dân cấp tỉnh có tuyến xe buýt đi qua để thống nhất thực hiện các nhiệm vụ nêu tại khoản 3 Điều 5 của Nghị định này. Thống nhất với Bộ Xây dựng trước khi mở tuyến xe buýt có điểm đầu hoặc điểm cuối nằm trong khu vực cảng hàng không.</t>
+          <t>Điều 15. Quyết định chỉ định</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Khoản 2 Điều 73</t>
+          <t>3. Quyết định chỉ định được gửi tới tổ chức được chỉ định, Chi cục Tiêu chuẩn Đo lường Chất lượng nơi tổ chức được chỉ định đăng ký trụ sở chính và đăng tải trên cổng thông tin điện tử của Tổng cục.</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>158/2024/NĐ-CP</t>
+          <t>Khoản 3 Điều 15</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=173412</t>
+          <t>24/2013/TT-BKHCN</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>claude-opus-5-5</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=37199</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>dat</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr"/>
+          <t>07/2024/TT-BKHCN</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>actor_has_transitional</t>
+        </is>
+      </c>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Khi Ủy ban nhân dân cấp tỉnh thực hiện nhiệm vụ quản lý vận tải đường bộ, cơ quan chuyên môn về giao thông ở địa phương được gọi tên theo sở nào?»; nhãn cũ khong_dat unanswerable_as_asked: Câu hỏi hỏi 'cơ quan chuyên môn về giao thông ở địa phương được gọi tên theo sở nào', nhưng khoản 2 không nói về sở; chỗ đổi là Bộ phải thống nhất trước khi mở tuyến xe buýt vào cảng hàng không (Bộ Giao thông vận tải → Bộ Xây dựng)). Câu hỏi hỏi bộ phải thống nhất, chạm chỗ đổi</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr"/>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Trường hợp một tổ chức được chỉ định kiểm định phương tiện đo, quyết định chỉ định được gửi tới những cơ quan nào?»; nhãn cũ khong_dat group_mismatch: Nơi nhận quyết định (tổ chức được chỉ định, Chi cục Tiêu chuẩn Đo lường Chất lượng) như nhau ở hai mốc; chỗ đổi chỉ là cổng thông tin đăng tải (Tổng cục → Ủy ban), câu hỏi không hỏi tới). Câu hỏi nay hỏi cả cổng đăng tải, chạm chỗ đổi Tổng cục → Ủy ban</t>
+        </is>
+      </c>
       <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>vilextime:T4:provision:fc79fb04-2c7e-11f1-9a1a-67adfcf2b37c:2024-11-21</t>
+          <t>vilextime:T4:provision:6d2c240a-ec3b-11f0-98fa-0d7f046b89cf:2024-11-22</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2990,66 +3486,82 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sau khi nhận văn bản thông báo kết quả đánh giá hồ sơ tuyển chọn nhiệm vụ của chương trình năng suất chất lượng, tổ chức được kiến nghị chủ trì phải hoàn thiện và gửi hồ sơ cho cơ quan nào trong thời hạn bao lâu?</t>
+          <t>Sau khi ban hành, quyết định chỉ định tổ chức kiểm định phương tiện đo được gửi tới đâu và được đăng tải trên cổng thông tin điện tử của cơ quan nào?</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Điều 19. Chuyên gia tư vấn độc lập đánh giá hồ sơ đăng ký tuyển chọn, giao trực tiếp thực hiện nhiệm vụ Việc đánh giá của chuyên gia tư vấn độc lập đối với hồ sơ đăng ký tuyển chọn, giao trực tiếp thực hiện nhiệm vụ được thực hiện theo quy định tại Điều 18, 19, 20 Chương IV Thông tư số 08/2017/TT-BKHCN. Áp dụng cụ thể đối với các nhiệm vụ thuộc Chương trình như sau:</t>
+          <t>2025-06-14 (giua_khoang)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>6. Trong thời hạn 10 ngày kể từ ngày nhận được văn bản thông báo của tổng cục Tiêu chuẩn Đo lường Chất lượng theo quy định tại khoản 5 Điều này, tổ chức được kiến nghị chủ trì thực hiện nhiệm vụ hoàn thiện và gửi hồ sơ cho Tổng cục Tiêu chuẩn Đo lường Chất lượng.</t>
+          <t>Điều 15. Quyết định chỉ định</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Khoản 6 Điều 19</t>
+          <t>3. Quyết định chỉ định được gửi tới tổ chức được chỉ định, Chi cục Tiêu chuẩn Đo lường Chất lượng nơi tổ chức được chỉ định đăng ký trụ sở chính và đăng tải trên cổng thông tin điện tử của Ủy ban.</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>15/2022/TT-BKHCN</t>
+          <t>Khoản 3 Điều 15</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=160095</t>
+          <t>24/2013/TT-BKHCN</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>claude-opus-5-5</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=37199</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>dat</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr"/>
+          <t>07/2024/TT-BKHCN</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>actor_has_transitional</t>
+        </is>
+      </c>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Một tổ chức nhận văn bản thông báo kết quả đánh giá hồ sơ tuyển chọn nhiệm vụ của chương trình năng suất chất lượng thì văn bản đó do cơ quan nào ban hành?»; nhãn cũ khong_dat group_mismatch: Văn bản thông báo vẫn là của 'tổng cục Tiêu chuẩn Đo lường Chất lượng' ở cả hai mốc (chữ viết thường nên lần thay tên không chạm tới); chỗ đổi là nơi nhận hồ sơ (Tổng cục → Ủy ban), câu hỏi không hỏi). Câu hỏi hỏi nơi nhận hồ sơ, chạm chỗ đổi</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr"/>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Trường hợp một tổ chức được chỉ định kiểm định phương tiện đo, quyết định chỉ định được gửi tới những cơ quan nào?»; nhãn cũ khong_dat group_mismatch: Nơi nhận quyết định (tổ chức được chỉ định, Chi cục Tiêu chuẩn Đo lường Chất lượng) như nhau ở hai mốc; chỗ đổi chỉ là cổng thông tin đăng tải (Tổng cục → Ủy ban), câu hỏi không hỏi tới). Câu hỏi nay hỏi cả cổng đăng tải, chạm chỗ đổi Tổng cục → Ủy ban</t>
+        </is>
+      </c>
       <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>vilextime:T4:provision:fc79fb04-2c7e-11f1-9a1a-67adfcf2b37c:2024-11-22</t>
+          <t>vilextime:T4:provision:6f540750-df45-11f0-bdb0-173fc9978251#k2#a:2015-09-30</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3059,61 +3571,2203 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sau khi nhận văn bản thông báo kết quả đánh giá hồ sơ tuyển chọn nhiệm vụ của chương trình năng suất chất lượng, tổ chức được kiến nghị chủ trì phải hoàn thiện và gửi hồ sơ cho cơ quan nào trong thời hạn bao lâu?</t>
+          <t>Khi Chấp hành viên của cơ quan thi hành án dân sự không thuộc quân đội gửi báo cáo thống kê kết quả thi hành án của kỳ trước cho Thủ trưởng cơ quan nơi công tác, thời hạn chậm nhất là trước ngày nào của kỳ báo cáo kế tiếp?</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2015-09-30</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Điều 19. Chuyên gia tư vấn độc lập đánh giá hồ sơ đăng ký tuyển chọn, giao trực tiếp thực hiện nhiệm vụ Việc đánh giá của chuyên gia tư vấn độc lập đối với hồ sơ đăng ký tuyển chọn, giao trực tiếp thực hiện nhiệm vụ được thực hiện theo quy định tại Điều 18, 19, 20 Chương IV Thông tư số 08/2017/TT-BKHCN. Áp dụng cụ thể đối với các nhiệm vụ thuộc Chương trình như sau:</t>
+          <t>2014-01-02 (giua_khoang)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>6. Trong thời hạn 10 ngày kể từ ngày nhận được văn bản thông báo của tổng cục Tiêu chuẩn Đo lường Chất lượng theo quy định tại khoản 5 Điều này, tổ chức được kiến nghị chủ trì thực hiện nhiệm vụ hoàn thiện và gửi hồ sơ cho Ủy ban Tiêu chuẩn Đo lường Chất lượng Quốc gia.</t>
+          <t>2. Thời hạn gửi báo cáo thống kê thi hành án dân sự:</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Khoản 6 Điều 19</t>
+          <t>a) Chậm nhất trước ngày 03 của kỳ báo cáo kế tiếp, Chấp hành viên gửi báo cáo thống kê kết quả thi hành án của kỳ trước cho Thủ trưởng cơ quan Thi hành án dân sự nơi công tác;</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>15/2022/TT-BKHCN</t>
+          <t>Điểm a Khoản 2 Điều 10</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=160095</t>
+          <t>01/2013/TT-BTP</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>claude-opus-5-5</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=30308</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>dat</t>
+          <t>08/2015/TT-BTP</t>
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Một tổ chức nhận văn bản thông báo kết quả đánh giá hồ sơ tuyển chọn nhiệm vụ của chương trình năng suất chất lượng thì văn bản đó do cơ quan nào ban hành?»; nhãn cũ khong_dat group_mismatch: Văn bản thông báo vẫn là của 'tổng cục Tiêu chuẩn Đo lường Chất lượng' ở cả hai mốc (chữ viết thường nên lần thay tên không chạm tới); chỗ đổi là nơi nhận hồ sơ (Tổng cục → Ủy ban), câu hỏi không hỏi). Câu hỏi hỏi nơi nhận hồ sơ, chạm chỗ đổi</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr"/>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Khi Chấp hành viên gửi báo cáo thống kê kết quả thi hành án của kỳ trước, thời hạn chậm nhất là trước ngày nào của kỳ báo cáo kế tiếp?»; nhãn cũ khong_dat question_ambiguous: Câu hỏi không phân biệt Chấp hành viên dân sự (điểm a) với Chấp hành viên thi hành án dân sự trong quân đội (điểm d, vẫn trước ngày 03); ở mốc 2 hai điểm cho hai đáp án khác nhau). Câu hỏi loại Chấp hành viên trong quân đội (điểm d)</t>
+        </is>
+      </c>
       <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>vilextime:T4:provision:6f540750-df45-11f0-bdb0-173fc9978251#k2#a:2015-10-01</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Khi Chấp hành viên của cơ quan thi hành án dân sự không thuộc quân đội gửi báo cáo thống kê kết quả thi hành án của kỳ trước cho Thủ trưởng cơ quan nơi công tác, thời hạn chậm nhất là trước ngày nào của kỳ báo cáo kế tiếp?</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2015-10-01</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2016-10-20 (giua_khoang)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2. Thời hạn gửi báo cáo thống kê thi hành án dân sự:</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>a) Chậm nhất trước ngày 02 của kỳ báo cáo kế tiếp, Chấp hành viên gửi báo cáo thống kê kết quả thi hành án của kỳ trước cho Thủ trưởng cơ quan Thi hành án dân sự nơi công tác;</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Điểm a Khoản 2 Điều 10</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>01/2013/TT-BTP</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=30308</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>08/2015/TT-BTP</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Khi Chấp hành viên gửi báo cáo thống kê kết quả thi hành án của kỳ trước, thời hạn chậm nhất là trước ngày nào của kỳ báo cáo kế tiếp?»; nhãn cũ khong_dat question_ambiguous: Câu hỏi không phân biệt Chấp hành viên dân sự (điểm a) với Chấp hành viên thi hành án dân sự trong quân đội (điểm d, vẫn trước ngày 03); ở mốc 2 hai điểm cho hai đáp án khác nhau). Câu hỏi loại Chấp hành viên trong quân đội (điểm d)</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>vilextime:T4:provision:6f603d84-e177-11f0-9fb9-2be267cb8d07:2024-12-19</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Theo quy định về đầu tư nâng cao năng lực, lực lượng cảnh sát nào được đầu tư cơ sở vật chất, phương tiện, thiết bị kỹ thuật để đấu tranh với tội phạm, vi phạm trong lĩnh vực môi trường?</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2024-12-19</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2018-04-19 (giua_khoang)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Điều 16. Đầu tư nâng cao năng lực cho Cảnh sát môi trường</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2. Cảnh sát môi trường được đầu tư cơ sở vật chất, trụ sở làm việc, phương tiện, thiết bị kỹ thuật đáp ứng yêu cầu công tác phòng, chống tội phạm và vi phạm hành chính về môi trường, tài nguyên, an toàn thực phẩm.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Khoản 2 Điều 16</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>105/2015/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=92155</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>157/2024/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Trường hợp đầu tư nâng cao năng lực cho Cảnh sát môi trường, lực lượng này được đầu tư những gì và để đáp ứng yêu cầu công tác nào?»; nhãn cũ khong_dat group_mismatch: Nội dung đầu tư và yêu cầu công tác như nhau ở hai mốc; chỉ đổi tên lực lượng). Câu hỏi hỏi tên lực lượng, không chép tên</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>vilextime:T4:provision:6f603d84-e177-11f0-9fb9-2be267cb8d07:2024-12-20</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Theo quy định về đầu tư nâng cao năng lực, lực lượng cảnh sát nào được đầu tư cơ sở vật chất, phương tiện, thiết bị kỹ thuật để đấu tranh với tội phạm, vi phạm trong lĩnh vực môi trường?</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2025-07-04 (giua_khoang)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Điều 16. Đầu tư nâng cao năng lực cho Cảnh sát môi trường</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2. lực lượng Cảnh sát phòng, chống tội phạm về môi trường được đầu tư cơ sở vật chất, trụ sở làm việc, phương tiện, thiết bị kỹ thuật đáp ứng yêu cầu công tác phòng, chống tội phạm và vi phạm hành chính về môi trường, tài nguyên, an toàn thực phẩm.</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Khoản 2 Điều 16</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>105/2015/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=92155</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>157/2024/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Trường hợp đầu tư nâng cao năng lực cho Cảnh sát môi trường, lực lượng này được đầu tư những gì và để đáp ứng yêu cầu công tác nào?»; nhãn cũ khong_dat group_mismatch: Nội dung đầu tư và yêu cầu công tác như nhau ở hai mốc; chỉ đổi tên lực lượng). Câu hỏi hỏi tên lực lượng, không chép tên</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>vilextime:T4:provision:76b4f67a-eb99-11f0-aeca-efd7a7c63751#k2#a:2018-12-31</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Khi xây dựng quy hoạch phát triển viễn thông quốc gia, quy hoạch phải phù hợp với những chiến lược, quy hoạch nào?</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2018-12-31</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2013-11-25 (giua_khoang)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2. Việc xây dựng quy hoạch phát triển viễn thông quốc gia được thực hiện theo các nguyên tắc sau đây:</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>a) Phù hợp với chiến lược, quy hoạch, kế hoạch phát triển kinh tế - xã hội của đất nước trong từng thời kỳ; tuân thủ pháp luật Việt Nam, điều ước quốc tế mà Cộng hòa xã hội chủ nghĩa Việt Nam là thành viên;</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Điểm a Khoản 2 Điều 8</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>41/2009/QH12</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=23776</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>21/2017/QH14</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>actor_has_transitional, split_effective_date</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>vilextime:T4:provision:76b4f67a-eb99-11f0-aeca-efd7a7c63751#k2#a:2019-01-01</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Khi xây dựng quy hoạch phát triển viễn thông quốc gia, quy hoạch phải phù hợp với những chiến lược, quy hoạch nào?</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2019-01-01</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2020-10-12 (giua_khoang)</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2. Việc xây dựng quy hoạch phát triển viễn thông quốc gia được thực hiện theo các nguyên tắc sau đây:</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>a) Phù hợp với chiến lược phát triển kinh tế - xã hội, quy hoạch cấp quốc gia, kế hoạch phát triển kinh tế - xã hội của đất nước trong từng thời kỳ; tuân thủ pháp luật Việt Nam, điều ước quốc tế mà Cộng hòa xã hội chủ nghĩa Việt Nam là thành viên;</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Điểm a Khoản 2 Điều 8</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>41/2009/QH12</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=23776</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>21/2017/QH14</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>actor_has_transitional, split_effective_date</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>vilextime:T4:provision:7ba0a2f8-eb88-11f0-a043-137cddd91168:2025-06-30</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Pháp luật về trợ cấp một lần cho chuyên gia giúp Lào và Campuchia quy định hồ sơ không hợp lệ được Sở Lao động - Thương binh và Xã hội chuyển trả cho cấp chính quyền nào?</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2018-10-02 (giua_khoang)</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>4. Ủy ban nhân dân cấp tỉnh chỉ đạo Sở Lao động - Thương binh và Xã hội</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>b) Kiểm tra tính hợp lệ của hồ sơ; chuyển trả hồ sơ không hợp lệ cho Ủy ban nhân dân cấp huyện để chuyển trả người nộp hồ sơ hoàn thiện;</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Điểm b Khoản 4 Điều 4</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>17/2014/TTLT-BLĐTBXH-BTC</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=37506</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>09/2025/TT-BNV</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>actor_has_transitional</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>document_ended 2025-07-01 bao_dong_gia</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>vilextime:T4:provision:7ba0a2f8-eb88-11f0-a043-137cddd91168:2025-07-01</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Pháp luật về trợ cấp một lần cho chuyên gia giúp Lào và Campuchia quy định hồ sơ không hợp lệ được Sở Lao động - Thương binh và Xã hội chuyển trả cho cấp chính quyền nào?</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2026-01-12 (giua_khoang)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>4. Ủy ban nhân dân cấp tỉnh chỉ đạo Sở Lao động - Thương binh và Xã hội</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>b) Kiểm tra tính hợp lệ của hồ sơ; chuyển trả hồ sơ không hợp lệ cho Ủy ban nhân dân cấp xã để chuyển trả người nộp hồ sơ hoàn thiện;</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Điểm b Khoản 4 Điều 4</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>17/2014/TTLT-BLĐTBXH-BTC</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=37506</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>09/2025/TT-BNV</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>actor_has_transitional</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>document_ended 2025-07-01 bao_dong_gia</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>vilextime:T4:provision:9d44166a-2e81-11f1-8975-ef6a7728f53c:2025-07-20</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Trường hợp cần hướng dẫn thực hiện chế độ cho đối tượng mới được bổ sung, những bộ nào phải ban hành thông tư liên tịch?</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2025-07-20</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2011-06-07 (giua_khoang)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Điều 3. Trách nhiệm thi hành</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2. Bộ Công an, Bộ Lao động - Thương binh và Xã hội, Bộ Tài chính ban hành Thông tư liên tịch hướng dẫn thực hiện chế độ đối với đối tượng quy định tại khoản 3 Điều 1 Nghị định này.</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Khoản 2 Điều 3</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>11/2011/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=26088</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>209/2025/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>vilextime:T4:provision:a324f2cc-df4c-11f0-894a-8ddf853d159d:2024-01-31</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Trong lĩnh vực quản lý rừng bền vững, Sở Nông nghiệp và Phát triển nông thôn phải báo cáo kết quả hằng năm trước ngày nào và gửi cho đơn vị nào thuộc Bộ?</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2024-01-31</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2022-08-01 (giua_khoang)</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>3. Sở Nông nghiệp và Phát triển nông thôn:</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>c) Hằng năm trước ngày 15 tháng 12, báo cáo Ủy ban nhân dân cấp tỉnh và Bộ Nông nghiệp và Phát triển nông thôn (Tổng cục Lâm nghiệp) kết quả xây dựng và thực hiện phương án quản lý rừng bền vững và cấp chứng chỉ quản lý rừng bền vững trên địa bàn tỉnh.</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Điểm c Khoản 3 Điều 18</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>28/2018/TT-BNNPTNT</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=133923</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>13/2023/TT-BNNPTNT</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>vilextime:T4:provision:ada68200-2d45-11f1-95b6-e35525714d94:2024-11-21</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Sau khi kế hoạch 5 năm xây dựng TCVN được phê duyệt, kế hoạch phải được công khai trên cổng thông tin điện tử của những cơ quan nào và trong thời hạn bao lâu?</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2022-02-24 (giua_khoang)</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2. Kế hoạch 5 năm xây dựng TCVN Nội dung kế hoạch 5 năm xây dựng TCVN bao gồm: lĩnh vực, đối tượng cụ thể cần xây dựng TCVN; loại tiêu chuẩn; số lượng TCVN cần xây dựng; thời gian thực hiện; nguồn kinh phí và kinh phí dự kiến. Lập, phê duyệt, điều chỉnh, bổ sung kế hoạch 5 năm xây dựng TCVN thực hiện theo trình tự sau đây:</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>c) Phê duyệt kế hoạch 5 năm Bộ trưởng Bộ Khoa học và Công nghệ tổ chức xem xét, phê duyệt kế hoạch 5 năm xây dựng TCVN. Bộ Khoa học và Công nghệ thông báo kế hoạch đã được phê duyệt đến các bộ, ngành, tổ chức liên quan và công khai trên Cổng thông tin điện tử của Bộ Khoa học và Công nghệ, Cổng thông tin điện tử của Tổng cục Tiêu chuẩn Đo lường Chất lượng trong thời hạn 30 (ba mươi) ngày, kể từ ngày kế hoạch được phê duyệt;</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Điểm c Khoản 2 Điều 4</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>11/2021/TT-BKHCN</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=152575</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>07/2024/TT-BKHCN</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>actor_has_transitional</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Pháp luật về xây dựng và áp dụng tiêu chuẩn quy định cơ quan nào phối hợp trong việc xây dựng và thông báo kế hoạch 5 năm xây dựng TCVN?»; nhãn cũ khong_dat question_ambiguous: 'Cơ quan nào phối hợp trong việc xây dựng và thông báo kế hoạch' không ghim được chỗ đổi (cổng thông tin công khai); điểm b cùng khoản giao Tổng cục lấy ý kiến, hoàn chỉnh dự thảo kế hoạch, và điểm c do Bộ trưởng phê duyệt, Bộ thông báo). Câu hỏi chốt việc công khai sau phê duyệt (điểm c), chạm chỗ đổi</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>vilextime:T4:provision:ada68200-2d45-11f1-95b6-e35525714d94:2024-11-22</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Sau khi kế hoạch 5 năm xây dựng TCVN được phê duyệt, kế hoạch phải được công khai trên cổng thông tin điện tử của những cơ quan nào và trong thời hạn bao lâu?</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2024-11-22</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2025-05-28 (giua_khoang)</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2. Kế hoạch 5 năm xây dựng TCVN Nội dung kế hoạch 5 năm xây dựng TCVN bao gồm: lĩnh vực, đối tượng cụ thể cần xây dựng TCVN; loại tiêu chuẩn; số lượng TCVN cần xây dựng; thời gian thực hiện; nguồn kinh phí và kinh phí dự kiến. Lập, phê duyệt, điều chỉnh, bổ sung kế hoạch 5 năm xây dựng TCVN thực hiện theo trình tự sau đây:</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>c) Phê duyệt kế hoạch 5 năm Bộ trưởng Bộ Khoa học và Công nghệ tổ chức xem xét, phê duyệt kế hoạch 5 năm xây dựng TCVN. Bộ Khoa học và Công nghệ thông báo kế hoạch đã được phê duyệt đến các bộ, ngành, tổ chức liên quan và công khai trên Cổng thông tin điện tử của Bộ Khoa học và Công nghệ, Cổng thông tin điện tử của Ủy ban Tiêu chuẩn Đo lường Chất lượng Quốc gia trong thời hạn 30 (ba mươi) ngày, kể từ ngày kế hoạch được phê duyệt;</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Điểm c Khoản 2 Điều 4</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>11/2021/TT-BKHCN</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=152575</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>07/2024/TT-BKHCN</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>actor_has_transitional</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Pháp luật về xây dựng và áp dụng tiêu chuẩn quy định cơ quan nào phối hợp trong việc xây dựng và thông báo kế hoạch 5 năm xây dựng TCVN?»; nhãn cũ khong_dat question_ambiguous: 'Cơ quan nào phối hợp trong việc xây dựng và thông báo kế hoạch' không ghim được chỗ đổi (cổng thông tin công khai); điểm b cùng khoản giao Tổng cục lấy ý kiến, hoàn chỉnh dự thảo kế hoạch, và điểm c do Bộ trưởng phê duyệt, Bộ thông báo). Câu hỏi chốt việc công khai sau phê duyệt (điểm c), chạm chỗ đổi</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>vilextime:T4:provision:adaff7e0-2d45-11f1-b065-b3402f7a0a1e:2024-11-21</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Trong lĩnh vực tiêu chuẩn quốc gia, tổ chức, cá nhân được xuất bản, phát hành TCVN khi có sự đồng ý bằng văn bản của cơ quan nào?</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2024-09-26 (giua_khoang)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2. Xuất bản và phát hành TCVN</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>đ) Tổ chức, cá nhân xuất bản, phát hành TCVN khi Tổng cục Tiêu chuẩn Đo lường Chất lượng đồng ý bằng văn bản.</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Điểm đ Khoản 2 Điều 9</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>11/2021/TT-BKHCN</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=152575</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>07/2024/TT-BKHCN</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>actor_has_transitional</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>vilextime:T4:provision:adaff7e0-2d45-11f1-b065-b3402f7a0a1e:2024-11-22</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Trong lĩnh vực tiêu chuẩn quốc gia, tổ chức, cá nhân được xuất bản, phát hành TCVN khi có sự đồng ý bằng văn bản của cơ quan nào?</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2024-11-22</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2025-01-28 (giua_khoang)</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2. Xuất bản và phát hành TCVN</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>đ) Tổ chức, cá nhân xuất bản, phát hành TCVN khi Ủy ban Tiêu chuẩn Đo lường Chất lượng Quốc gia đồng ý bằng văn bản.</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Điểm đ Khoản 2 Điều 9</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>11/2021/TT-BKHCN</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=152575</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>07/2024/TT-BKHCN</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>actor_has_transitional</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>vilextime:T4:provision:bcce4ee0-2f37-11f1-927e-c7ac35ffa800:2024-11-14</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Thẩm quyền áp dụng biện pháp khắc phục hậu quả của Chủ tịch Ủy ban nhân dân cấp huyện trong lĩnh vực bổ trợ tư pháp được xác định ra sao?</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2022-09-24 (giua_khoang)</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2. Chủ tịch Ủy ban nhân dân cấp huyện có quyền:</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>d) Áp dụng biện pháp khắc phục hậu quả quy định tại các điểm a, e và i khoản 1 Điều 28 Luật Xử lý vi phạm hành chính; các điểm a, b, đ, l, m và n khoản 3 Điều 3 Nghị định này.</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Điểm d Khoản 2 Điều 83</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>82/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=143024</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>117/2024/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>cap_huyen 2026-01-23 chờ</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>vilextime:T4:provision:bdb196ac-df3f-11f0-a53b-49fbe419b389:2025-06-22</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Khi hoạt động của bãi cất, hạ cánh trên boong tàu vi phạm điều kiện, quyết định đóng bãi phải được thông báo cho những bộ nào?</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2018-03-08 (giua_khoang); 2026-08-17 (sau_het_hieu_luc)</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Điều 16. Trình tự, thủ tục đóng bãi cất, hạ cánh trên boong tàu</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>3. Khi hoạt động của bãi cất, hạ cánh vi phạm một trong các điều kiện quy định tại điểm a, b, c, d, đ của khoản 2 Điều 10; Bộ Tổng Tham mưu ra quyết định đóng bãi cất, hạ cánh và thông báo với Bộ Giao thông vận tải, chủ sở hữu tàu và các cơ quan, tổ chức, cá nhân liên quan.</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Khoản 3 Điều 16</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>42/2016/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=141668</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>101/2025/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>actor_has_transitional</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>vilextime:T4:provision:bdb196ac-df3f-11f0-a53b-49fbe419b389:2025-06-23</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Khi hoạt động của bãi cất, hạ cánh trên boong tàu vi phạm điều kiện, quyết định đóng bãi phải được thông báo cho những bộ nào?</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2025-11-12 (giua_khoang)</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Điều 16. Trình tự, thủ tục đóng bãi cất, hạ cánh trên boong tàu</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>3. Khi hoạt động của bãi cất, hạ cánh vi phạm một trong các điều kiện quy định tại điểm a, b, c, d, đ của khoản 2 Điều 10; Bộ Tổng Tham mưu ra quyết định đóng bãi cất, hạ cánh và thông báo với Bộ Xây dựng, chủ sở hữu tàu và các cơ quan, tổ chức, cá nhân liên quan.</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Khoản 3 Điều 16</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>42/2016/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=141668</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>101/2025/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>actor_has_transitional</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>vilextime:T4:provision:c1badfb0-1ef0-11f1-916f-cb5282846544:2026-01-25</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Pháp luật về bảo tồn các vùng đất ngập nước quy định các bộ, cơ quan ngang bộ khác phải phối hợp với bộ nào để thực hiện quy định về bảo tồn?</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2023-10-14 (giua_khoang)</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Điều 31. Trách nhiệm của các cơ quan cấp bộ</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>5. Các bộ, cơ quan ngang bộ khác trong phạm vi nhiệm vụ, quyền hạn được giao, phối hợp với Bộ Tài nguyên và Môi trường thực hiện các quy định về bảo tồn và sử dụng bền vững các vùng đất ngập nước theo Nghị định này và pháp luật có liên quan.</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Khoản 5 Điều 31</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>66/2019/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=136645</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>43/2026/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>actor_has_transitional</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>vilextime:T4:provision:c1badfb0-1ef0-11f1-916f-cb5282846544:2026-01-26</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Pháp luật về bảo tồn các vùng đất ngập nước quy định các bộ, cơ quan ngang bộ khác phải phối hợp với bộ nào để thực hiện quy định về bảo tồn?</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2026-05-20 (giua_khoang)</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Điều 31. Trách nhiệm của các cơ quan cấp bộ</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>5. Các bộ, cơ quan ngang bộ khác trong phạm vi nhiệm vụ, quyền hạn được giao, phối hợp với Bộ Nông nghiệp và Môi trường thực hiện các quy định về bảo tồn và sử dụng bền vững các vùng đất ngập nước theo Nghị định này và pháp luật có liên quan.</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Khoản 5 Điều 31</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>66/2019/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=136645</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>43/2026/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>actor_has_transitional</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>vilextime:T4:provision:d3fc108c-eb78-11f0-9da0-edb19ede6132:2025-08-14</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Thẩm quyền phê duyệt phương án đấu giá quyền sử dụng đất thuộc thẩm quyền giao đất của cấp tỉnh được xác định ra sao?</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>2024-12-10 (giua_khoang)</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>4. Thẩm định, phê duyệt phương án đấu giá quyền sử dụng đất</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>b) Trường hợp đấu giá quyền sử dụng đất thuộc thẩm quyền giao đất, cho thuê đất của Ủy ban nhân dân cấp tỉnh thì cơ quan có chức năng quản lý đất đai cấp tỉnh kiểm tra, hoàn thiện hồ sơ trình Ủy ban nhân dân cấp tỉnh phê duyệt phương án đấu giá quyền sử dụng đất.</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Điểm b Khoản 4 Điều 55</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>102/2024/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=169363</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>226/2025/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>actor_has_transitional, split_effective_date</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>document_ended 2025-07-01 bao_dong_gia</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr"/>
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>vilextime:T4:provision:d3fc108c-eb78-11f0-9da0-edb19ede6132:2025-08-15</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Thẩm quyền phê duyệt phương án đấu giá quyền sử dụng đất thuộc thẩm quyền giao đất của cấp tỉnh được xác định ra sao?</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2026-01-26 (giua_khoang)</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>4. Thẩm định, phê duyệt phương án đấu giá quyền sử dụng đất</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>b) Trường hợp đấu giá quyền sử dụng đất thuộc thẩm quyền giao đất, cho thuê đất của Chủ tịch Ủy ban nhân dân cấp tỉnh thì cơ quan có chức năng quản lý đất đai cấp tỉnh kiểm tra, hoàn thiện hồ sơ trình Chủ tịch Ủy ban nhân dân cấp tỉnh phê duyệt phương án đấu giá quyền sử dụng đất.</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Điểm b Khoản 4 Điều 55</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>102/2024/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=169363</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>226/2025/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>actor_has_transitional, split_effective_date</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>document_ended 2025-07-01 bao_dong_gia</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>vilextime:T4:provision:dcf457d0-3b96-11f1-b174-b5c1cf7b0c30:2026-08-09</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Trước khi mở tuyến xe buýt đi đến hoặc xuất phát từ khu vực cảng hàng không, Ủy ban nhân dân cấp tỉnh phải thống nhất với bộ nào?</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2025-06-17 (giua_khoang)</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Điều 73. Ủy ban nhân dân cấp tỉnh</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2. Phối hợp với Ủy ban nhân dân cấp tỉnh có tuyến xe buýt đi qua để thống nhất thực hiện các nhiệm vụ nêu tại khoản 3 Điều 5 của Nghị định này. Thống nhất với Bộ Giao thông vận tải trước khi mở tuyến xe buýt có điểm đầu hoặc điểm cuối nằm trong khu vực cảng hàng không.</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Khoản 2 Điều 73</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>158/2024/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=173412</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>218/2026/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Khi Ủy ban nhân dân cấp tỉnh thực hiện nhiệm vụ quản lý vận tải đường bộ, cơ quan chuyên môn về giao thông ở địa phương được gọi tên theo sở nào?»; nhãn cũ khong_dat unanswerable_as_asked: Câu hỏi hỏi 'cơ quan chuyên môn về giao thông ở địa phương được gọi tên theo sở nào', nhưng khoản 2 không nói về sở; chỗ đổi là Bộ phải thống nhất trước khi mở tuyến xe buýt vào cảng hàng không (Bộ Giao thông vận tải → Bộ Xây dựng)). Câu hỏi hỏi bộ phải thống nhất, chạm chỗ đổi</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr"/>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>vilextime:T4:provision:dcf457d0-3b96-11f1-b174-b5c1cf7b0c30:2026-08-10</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Trước khi mở tuyến xe buýt đi đến hoặc xuất phát từ khu vực cảng hàng không, Ủy ban nhân dân cấp tỉnh phải thống nhất với bộ nào?</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>2026-08-29 (giua_khoang)</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Điều 73. Ủy ban nhân dân cấp tỉnh</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2. Phối hợp với Ủy ban nhân dân cấp tỉnh có tuyến xe buýt đi qua để thống nhất thực hiện các nhiệm vụ nêu tại khoản 3 Điều 5 của Nghị định này. Thống nhất với Bộ Xây dựng trước khi mở tuyến xe buýt có điểm đầu hoặc điểm cuối nằm trong khu vực cảng hàng không.</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Khoản 2 Điều 73</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>158/2024/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=173412</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>218/2026/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Khi Ủy ban nhân dân cấp tỉnh thực hiện nhiệm vụ quản lý vận tải đường bộ, cơ quan chuyên môn về giao thông ở địa phương được gọi tên theo sở nào?»; nhãn cũ khong_dat unanswerable_as_asked: Câu hỏi hỏi 'cơ quan chuyên môn về giao thông ở địa phương được gọi tên theo sở nào', nhưng khoản 2 không nói về sở; chỗ đổi là Bộ phải thống nhất trước khi mở tuyến xe buýt vào cảng hàng không (Bộ Giao thông vận tải → Bộ Xây dựng)). Câu hỏi hỏi bộ phải thống nhất, chạm chỗ đổi</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>vilextime:T4:provision:e902d3ee-df52-11f0-a71c-af726f757a17:2021-12-31</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Pháp luật về xử phạt vi phạm hành chính trong lĩnh vực giáo dục quy định Chánh Thanh tra cơ quan chuyên môn về giáo dục cấp tỉnh được phạt tiền tối đa bao nhiêu?</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2021-12-31</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2021-08-18 (giua_khoang)</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2. Chánh Thanh tra cơ quan chuyên môn về giáo dục thuộc Ủy ban nhân dân cấp tỉnh, Trưởng đoàn thanh tra chuyên ngành trong lĩnh vực giáo dục cấp Sở có quyền:</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>b) Phạt tiền đến 50.000.000 đồng;</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Điểm b Khoản 2 Điều 37</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>04/2021/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=148174</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>127/2021/nđ-cp</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>actor_has_transitional</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
+      <c r="S62" t="inlineStr"/>
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr"/>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>vilextime:T4:provision:e902d3ee-df52-11f0-a71c-af726f757a17:2022-01-01</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Pháp luật về xử phạt vi phạm hành chính trong lĩnh vực giáo dục quy định Chánh Thanh tra cơ quan chuyên môn về giáo dục cấp tỉnh được phạt tiền tối đa bao nhiêu?</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2026-01-19 (giua_khoang)</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2. Chánh Thanh tra cơ quan chuyên môn về giáo dục thuộc Ủy ban nhân dân cấp tỉnh, Trưởng đoàn thanh tra chuyên ngành của Sở Giáo dục và Đào tạo có quyền:</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>b) Phạt tiền đến 75.000.000 đồng;</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Điểm b Khoản 2 Điều 37</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>04/2021/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=148174</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>127/2021/nđ-cp</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>actor_has_transitional</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr"/>
+      <c r="S63" t="inlineStr"/>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr"/>
+      <c r="V63" t="inlineStr"/>
+      <c r="W63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>vilextime:T4:provision:fc79fb04-2c7e-11f1-9a1a-67adfcf2b37c:2024-11-21</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Sau khi nhận văn bản thông báo kết quả đánh giá hồ sơ tuyển chọn nhiệm vụ của chương trình năng suất chất lượng, tổ chức được kiến nghị chủ trì phải hoàn thiện và gửi hồ sơ cho cơ quan nào trong thời hạn bao lâu?</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>2024-08-01 (giua_khoang)</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Điều 19. Chuyên gia tư vấn độc lập đánh giá hồ sơ đăng ký tuyển chọn, giao trực tiếp thực hiện nhiệm vụ Việc đánh giá của chuyên gia tư vấn độc lập đối với hồ sơ đăng ký tuyển chọn, giao trực tiếp thực hiện nhiệm vụ được thực hiện theo quy định tại Điều 18, 19, 20 Chương IV Thông tư số 08/2017/TT-BKHCN. Áp dụng cụ thể đối với các nhiệm vụ thuộc Chương trình như sau:</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>6. Trong thời hạn 10 ngày kể từ ngày nhận được văn bản thông báo của tổng cục Tiêu chuẩn Đo lường Chất lượng theo quy định tại khoản 5 Điều này, tổ chức được kiến nghị chủ trì thực hiện nhiệm vụ hoàn thiện và gửi hồ sơ cho Tổng cục Tiêu chuẩn Đo lường Chất lượng.</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Khoản 6 Điều 19</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>15/2022/TT-BKHCN</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=160095</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>07/2024/TT-BKHCN</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>actor_has_transitional</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Một tổ chức nhận văn bản thông báo kết quả đánh giá hồ sơ tuyển chọn nhiệm vụ của chương trình năng suất chất lượng thì văn bản đó do cơ quan nào ban hành?»; nhãn cũ khong_dat group_mismatch: Văn bản thông báo vẫn là của 'tổng cục Tiêu chuẩn Đo lường Chất lượng' ở cả hai mốc (chữ viết thường nên lần thay tên không chạm tới); chỗ đổi là nơi nhận hồ sơ (Tổng cục → Ủy ban), câu hỏi không hỏi). Câu hỏi hỏi nơi nhận hồ sơ, chạm chỗ đổi</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr"/>
+      <c r="T64" t="inlineStr"/>
+      <c r="U64" t="inlineStr"/>
+      <c r="V64" t="inlineStr"/>
+      <c r="W64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>vilextime:T4:provision:fc79fb04-2c7e-11f1-9a1a-67adfcf2b37c:2024-11-22</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Sau khi nhận văn bản thông báo kết quả đánh giá hồ sơ tuyển chọn nhiệm vụ của chương trình năng suất chất lượng, tổ chức được kiến nghị chủ trì phải hoàn thiện và gửi hồ sơ cho cơ quan nào trong thời hạn bao lâu?</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2024-11-22</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>2025-01-24 (giua_khoang)</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Điều 19. Chuyên gia tư vấn độc lập đánh giá hồ sơ đăng ký tuyển chọn, giao trực tiếp thực hiện nhiệm vụ Việc đánh giá của chuyên gia tư vấn độc lập đối với hồ sơ đăng ký tuyển chọn, giao trực tiếp thực hiện nhiệm vụ được thực hiện theo quy định tại Điều 18, 19, 20 Chương IV Thông tư số 08/2017/TT-BKHCN. Áp dụng cụ thể đối với các nhiệm vụ thuộc Chương trình như sau:</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>6. Trong thời hạn 10 ngày kể từ ngày nhận được văn bản thông báo của tổng cục Tiêu chuẩn Đo lường Chất lượng theo quy định tại khoản 5 Điều này, tổ chức được kiến nghị chủ trì thực hiện nhiệm vụ hoàn thiện và gửi hồ sơ cho Ủy ban Tiêu chuẩn Đo lường Chất lượng Quốc gia.</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Khoản 6 Điều 19</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>15/2022/TT-BKHCN</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=160095</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>07/2024/TT-BKHCN</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>actor_has_transitional</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Một tổ chức nhận văn bản thông báo kết quả đánh giá hồ sơ tuyển chọn nhiệm vụ của chương trình năng suất chất lượng thì văn bản đó do cơ quan nào ban hành?»; nhãn cũ khong_dat group_mismatch: Văn bản thông báo vẫn là của 'tổng cục Tiêu chuẩn Đo lường Chất lượng' ở cả hai mốc (chữ viết thường nên lần thay tên không chạm tới); chỗ đổi là nơi nhận hồ sơ (Tổng cục → Ủy ban), câu hỏi không hỏi). Câu hỏi hỏi nơi nhận hồ sơ, chạm chỗ đổi</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr"/>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
+      <c r="V65" t="inlineStr"/>
+      <c r="W65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
